--- a/Inputs/Canada_LNG_Asset_Register.xlsx
+++ b/Inputs/Canada_LNG_Asset_Register.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20 10:00 UTC</t>
+          <t>2026-09-27 (register update, see REGISTER UPDATE 27 SEP 2026 below). Previous build 2026-08-20 10:00 UTC.</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>All Canadian LNG terminals in GEM GGIT (Sep 2025), plus projects not in GEM found by research: Summit Lake PG LNG, Kino Aski LNG (formerly Marinvest Baie-Comeau), the Tilbury Marine Jetty, and Kanata LNG. Discovery LNG is in GEM but was moved from inactive to early_proposed pending verification.</t>
+          <t>All Canadian LNG terminals in GEM GGIT (Sep 2025), plus projects not in GEM found by research: Summit Lake PG LNG, Kino Aski LNG (formerly Marinvest Baie-Comeau), the Tilbury Marine Jetty, and Kanata LNG. Discovery LNG is in GEM as cancelled and the register matches (1 Sep 2026).</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Announced, but no completed regulatory filing. Groups with advanced_proposed as proposed in the calculation, but the tier is retained so the difference in maturity stays visible. Capacity figures here are weaker: Kino Aski's 15 mtpa is a proponent press release, not a filed figure, and Summit Lake's 2.7 is an upper bound from a suspended assessment.</t>
+          <t>Announced, but no completed regulatory filing. Groups with advanced_proposed as proposed in the calculation, but the tier is retained so the difference in maturity stays visible. Capacity figures here are weaker: Kino Aski's 15 mtpa is a developer press release and Fermeuse's 10 mtpa a developer statement to journalists, neither a filed figure, and Summit Lake's 2.7 is an upper bound from a suspended assessment.</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Not a live export proposal. Kept visible so it is not forgotten. This describes progress as an export project, not whether the asset is running: Saint John is in watch but is operating, and its calc_group says so.</t>
+          <t>Not a live export proposal. Kept visible so it is not forgotten. This describes progress as an export project, not whether the asset is running: Saint John is in watch but is operating, and its calc_group says so. Kitimat LNG is in watch too: a permitted site held by the Haisla Nation with no live proposal. Northern Prince LNG and the Churchill and Port Nelson Hudson Bay LNG concepts are also watch rows.</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>The standard is nameplate</t>
+          <t>The standard is the latest design figure</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>capacity_mtpa records nameplate design capacity, what the facility is engineered to produce. This matches how proponents pitch projects, the framing the brief asks us to use.</t>
+          <t>capacity_mtpa records the most recent design capacity published by the developer or permitted by a regulator. Where a regulator has permitted more than the original nameplate from the same equipment, the permitted figure is used (decision of 27 Sep 2026: use the latest available data).</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Where sources give different figures, the nameplate is used and the alternative is stated in capacity_basis. Cedar LNG: the proponent's FID announcement states a nameplate of 3.3 mtpa, while NRCan and CER publish 3.0. The register carries 3.3, with 3.0 recorded as a licenced or rounded figure.</t>
+          <t>Where sources give different figures, the latest design figure is used and the others are stated in capacity_basis. Cedar LNG: the FID announcement stated 3.3 mtpa and NRCan and the CER publish 3.0, but the BC EAO's amended certificate of July 2026 permits 3.75 mtpa from the same equipment. The register carries 3.75.</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Kino Aski's 15 mtpa is from the proponent's 17 August 2026 press release rather than a filed project description; the earlier 10 mtpa journalist statement is replaced. The feedgas pipeline route is undefined. Summit Lake's 2.7 is an upper bound from its impact assessment. Both are flagged in capacity_basis.</t>
+          <t>Kino Aski's 15 mtpa is from the developer's 17 August 2026 press release rather than a filed project description; the earlier 10 mtpa journalist statement is replaced. Its feedgas route is undefined, though the developer now names Western Canadian gas. Fermeuse's 10 mtpa is a developer statement to The Narwhal (March 2026). Summit Lake's 2.7 is an upper bound from its impact assessment. All are flagged in capacity_basis.</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>LNG Canada GL-330, Woodfibre GL-340, Ksi Lisims GL-346, Cedar GL-349 issued January 2026. Counting conservatively from issue date those authorise exports to 2056, 2057, 2063 and 2066. Canada's legislated net-zero date is 2050. Every one is past it.</t>
+          <t>LNG Canada GL-330, Woodfibre GL-340, Ksi Lisims GL-346, Cedar GL-349 issued January 2026. Counting conservatively from issue date those authorise exports to 2056, 2057, 2063 and 2066. Canada's legislated net-zero date is 2050. Every one is past it. Ksi Lisims' licence also ends early if exports have not begun within 10 years of issue (GEM).</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>A licence term is not an operating life: licences are renewable and Tilbury has run since 1971. The CER may issue LNG licences for up to 50 years, so 40 is not a ceiling. The 30/40/50 sensitivity lives in the Data Inputs file.</t>
+          <t>A licence term is not an operating life: licences are renewable and Tilbury has run since 1971. Since Bill C-15 received royal assent on 26 March 2026, LNG export licences can run for up to 50 years (Major Projects Office: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html), so 40 is not a ceiling. The 30/40/50 sensitivity lives in the Data Inputs file.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>All 45.4 mtpa of active export capacity supplies zero LNG to the Canadian domestic market. Canada already meets domestic demand by pipeline. Yet upstream, pipeline and liquefaction emissions, about 29 per cent of the lifecycle total, land on Canada's own inventory. The remaining 71 per cent is counted by the importing country.</t>
+          <t>All 45.85 mtpa of active export capacity supplies zero LNG to the Canadian domestic market. Canada already meets domestic demand by pipeline. Yet upstream, pipeline and liquefaction emissions, about 29 per cent of the lifecycle total, land on Canada's own inventory. The remaining 71 per cent is counted by the importing country.</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>It carries 21.46 bcm/y and already serves 23.87 from LNG Canada Phase 1 plus Cedar, whose 8 km connector draws on it. Phase 2's 14 mtpa, 31 per cent of live export capacity, depends on the proposed second line agreed only in principle in March 2026.</t>
+          <t>It carries 21.46 bcm/y and already serves 24.50 from LNG Canada Phase 1 plus Cedar (3.75 mtpa since the July 2026 certificate amendment), whose 8 km connector draws on it. Phase 2's 14 mtpa, 31 per cent of live export capacity, depends on the proposed second line agreed only in principle in March 2026.</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>69.78 bcm/y of live pipeline capacity against 62.65 of demand looks comfortable, but capacity is not fungible. Spare room on Prince Rupert Gas Transmission cannot serve Kitimat. Only the per-line check tells you anything.</t>
+          <t>69.78 bcm/y of live pipeline capacity against 63.28 of demand looks comfortable, but capacity is not fungible. Spare room on Prince Rupert Gas Transmission cannot serve Kitimat. Only the per-line check tells you anything.</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fermeuse capacity is derived</t>
+          <t>Fermeuse capacity is a developer statement</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fermeuse Energy has not published a liquefaction capacity. The register records 4.5 mtpa, derived from the stated 9.7 Tcf Jeanne d'Arc resource over a 40-year life, net of the gas liquefaction burns as fuel. The derivation is conditional on the proponent's resource claim and assumes full recovery on a flat profile, both of which push it up; it is not a lower bound. This is an exception to the nameplate convention and is flagged in capacity_basis.</t>
+          <t>Crown LNG's chief executive told The Narwhal (19 Mar 2026) the plant would export up to 10 mtpa, and the register carries 10. No filing states it. The operating life is derived instead: the developer's 9.7 Tcf Jeanne d'Arc resource lasts about 18 years at 10 mtpa, net of liquefaction fuel, recorded in project_life_years. The earlier 4.5 mtpa derivation over a 40-year life is superseded and kept as history in capacity_basis.</t>
         </is>
       </c>
     </row>
@@ -1021,6 +1021,230 @@
       <c r="B56" t="inlineStr">
         <is>
           <t>liquefaction_drive is gas_turbine for every export and bunkering asset. Previous electric_committed / electric_planned / not_published classifications are retained in liquefaction_drive_note, prefixed with 'previously classified as'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>REGISTER UPDATE 27 SEP 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Not yet run</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>The model has not been re-run on this register. Every result in the repo README and Outputs is still the 3 September 2026 lock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LNG Canada Phase 2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>No FID yet. Status text refreshed; first LNG 2030 reconfirmed (GEM wiki, 25 Sep 2026: https://www.gem.wiki/LNG_Canada_Terminal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ksi Lisims</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>first_export_year 2029 to 2032 (Uniper agreement, https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html); offtake 4 to 8 mtpa; licence early-expiry clause; grid timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Fermeuse</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>capacity 4.5 to 10 mtpa (developer statement, https://thenarwhal.ca/lng-newfoundland-lessons-kitimat-bc/); project_life_years 18, derived from the developer's resource.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cedar</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>capacity 3.3 to 3.75 mtpa (BC EAO amended certificate, July 2026: https://projects.eao.gov.bc.ca/api/public/document/68caf0067a03b4002205daf9/download/Cedar%20LNG%20Accommodation%20+%20Capacity%20Amendment%20Application.pdf). Coastal GasLink demand and headroom updated to match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Kino Aski</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>feedgas basin Western Canada (developer-stated: https://kinoaskilng.ca/); drive, cost and commercial notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Kanata</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Indicative terms with Hanwha, pre-FEED, FID targeted early 2028 (https://www.lngindustry.com/floating-lng/14092026/kanata-clean-power-and-hanwha-ocean-to-launch-pre-feed-for-proposed-floating-lng-project/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Woodfibre</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>first_export_year 2028 to 2027 (developer targets end-2027 in service: https://lngjournal.com/index.php/latest-news-mainmenu-47/item/116798-woodfibre-lng-on-track-to-complete-construction-by-late-2027); GL-340 deadline June 2030; expansion noted, capacity unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tilbury Phase 2</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Certificate and federal decision 21 Sep 2026 (https://www.canada.ca/en/impact-assessment-agency/news/2026/09/major-milestone-completed.html); 2.5 mtpa confirmed as an addition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Tilbury Phase 1b</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>first_export_year 2028 to 2031 (https://news.gov.bc.ca/releases/2026ECS0043-000870).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tilbury Marine Jetty</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Proponent named: Tilbury Jetty Limited Partnership (https://tilburypacific.ca/about-tilbury-pacific/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Kitimat LNG</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Owner yáqʷa Development Corporation (Haisla Nation) (https://www.yaqwadevcorp.com/2025/11/18/yaq%CA%B7a-acquisition/); inactive to watch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Placentia Bay</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EA registration 2177 still Active (https://www.gov.nl.ca/ecc/env-assessment/projects-list/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NRCan's 6.5 mtpa import capacity recorded against GEM's 7.5 (https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Tamaska</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Owner's current name: Cryopeak Energy Solutions (https://www.cryopeak.com/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kitsault: the BusinessWire releases on a multi-commodity port could not be opened (404), so no change was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FID delay flag</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>New field first_export_year_assumes_fid. Where True, the model does not add the five-year FID delay to a pre-FID asset because its first_export_year already allows for the build: Ksi Lisims (2032, Uniper agreement: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html) and Tilbury Phase 1b (2031, https://news.gov.bc.ca/releases/2026ECS0043-000870).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>New rows 27 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG, Port of Churchill Plus LNG and NeeStaNan Port Nelson added as watch rows (excluded from all totals); Project Northern Lights added as a domestic row with no published capacity (enters no total). Dawson Creek, Elmworth, Hagar and Linde held until sources confirm them.</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF57"/>
+  <dimension ref="A1:BG61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1092,6 +1316,8 @@
     <col width="46" customWidth="1" min="52" max="52"/>
     <col width="50" customWidth="1" min="53" max="53"/>
     <col width="90" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1385,6 +1611,11 @@
           <t>gem_status_date</t>
         </is>
       </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>first_export_year_assumes_fid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2321,12 +2552,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cryopeak LNG Solutions</t>
+          <t>Cryopeak Energy Solutions</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Cryopeak LNG Solutions</t>
+          <t>Cryopeak Energy Solutions</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2336,7 +2567,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2434,7 +2665,7 @@
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
+          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Cryopeak Energy Solutions: https://www.cryopeak.com/</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2841,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Positive FID June 2024; early construction underway.</t>
+          <t>Positive FID June 2024. FLNG vessel more than 50% complete at Samsung Heavy Industries (April 2026) and due at Kitimat in 2028; in service expected late 2028.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2635,7 +2866,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N9" t="b">
@@ -2655,11 +2886,11 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>nameplate design capacity, confirmed by the proponent's own FID announcement. NRCan and CER both cite 3.0 mtpa, which appears to be a rounded or licenced figure rather than nameplate.</t>
+          <t>Latest permitted design throughput: 3.75 mtpa (500 mmscfd) under the BC EAO's amended certificate of July 2026, from efficiencies with the same equipment, still subject to IAAC and BC Energy Regulator approval. Earlier figures: 3.3 mtpa in the developer's FID announcement (June 2024); 3.0 mtpa (400 mmscfd) from NRCan and the CER, the pre-amendment design basis.</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
@@ -2693,7 +2924,7 @@
         <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.455</v>
+        <v>0.4</v>
       </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
@@ -2801,7 +3032,7 @@
       <c r="BA9" s="4" t="inlineStr"/>
       <c r="BB9" s="4" t="inlineStr">
         <is>
-          <t>Cedar LNG FID announcement (25 Jun 2024): https://www.cedarlng.com/cedar-lng-announces-positive-final-investment-decision/ | GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | National Observer, LNG Canada grid connection cost: https://www.nationalobserver.com/2025/10/07/news/lng-canada-hydro-connection-cost | GEM wiki: https://www.gem.wiki/Cedar_FLNG_Terminal</t>
+          <t>Cedar LNG FID announcement (25 Jun 2024): https://www.cedarlng.com/cedar-lng-announces-positive-final-investment-decision/ | GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | National Observer, LNG Canada grid connection cost: https://www.nationalobserver.com/2025/10/07/news/lng-canada-hydro-connection-cost | GEM wiki: https://www.gem.wiki/Cedar_FLNG_Terminal | BC EAO, Cedar LNG capacity amendment application: https://projects.eao.gov.bc.ca/api/public/document/68caf0067a03b4002205daf9/download/Cedar%20LNG%20Accommodation%20+%20Capacity%20Amendment%20Application.pdf | Canadian Vanguard, Cedar LNG secures BC regulatory nod (Jul 2026): https://www.thecanadianvanguard.com/cedar-lng-secures-bc-regulatory-nod-to-expand-future-output-capacity/ | GIIGNL, Cedar LNG receives approval to increase project capacity (22 Jul 2026): https://www.giignl.org/news/cedar-lng-receives-approval-to-increase-project-capacity | Pembina, 2026 guidance and Cedar update (15 Dec 2025): https://www.pembina.com/media-centre/news/details/26400a51-ee23-4209-b789-4a15c2f699d1 | Cedar LNG spring 2026 newsletter: https://www.cedarlng.com/2026/04/30/spring-2026-newsletter/</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -2848,7 +3079,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Under construction; BC Hydro interconnection works scheduled 2026-2027.</t>
+          <t>Under construction and more than halfway complete (July 2026); in service targeted for end-2027. BC Hydro interconnection works scheduled 2026-2027.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2878,7 +3109,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N10" t="b">
@@ -2890,11 +3121,11 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>GL-340, 40 year term, issued 2017 (AO-001-GL-340, 2023). Earlier 25 year GL-304 revoked 2017.</t>
+          <t>GL-340, 40 year term, issued 2017 (AO-001-GL-340, 2023). Earlier 25 year GL-304 revoked 2017. The CER extended the deadline for first exports under GL-340 from June 2027 to June 2030 (Aug 2025).</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -2950,7 +3181,7 @@
       </c>
       <c r="AE10" s="4" t="inlineStr">
         <is>
-          <t>100% of capacity contracted</t>
+          <t>100% of capacity contracted. A phased expansion from 2.1 to 2.5 mtpa (listed capex US$9.9B, 'Concept' stage) appears in the federal Canada Investment Summit Prospectus (Sep 2026). No filing located, so capacity stays at the 2.1 nameplate.</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -3004,7 +3235,7 @@
       </c>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>GL-340, 40 year term, issued 9 Jun 2017 (AO-001-GL-340, 2023). Earlier 25 year GL-304 revoked 2017.</t>
+          <t>GL-340, 40 year term, issued 9 Jun 2017 (AO-001-GL-340, 2023). Earlier 25 year GL-304 revoked 2017. The CER extended the deadline for first exports under GL-340 from June 2027 to June 2030 (Aug 2025).</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -3047,7 +3278,7 @@
       </c>
       <c r="BB10" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Squamish Chief, Woodfibre issues Notice to Proceed (Apr 2022): https://www.squamishchief.com/local-news/wlng-says-it-has-given-the-final-green-light-for-construction-5283923 | Enbridge Woodfibre LNG project page: https://www.enbridge.com/projects-and-infrastructure/projects/woodfibre-lng | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | BC Hydro Woodfibre LNG interconnection: https://www.bchydro.com/energy-in-bc/projects/woodfibrelng.html | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki Woodfibre LNG Terminal: https://www.gem.wiki/Woodfibre_LNG_Terminal</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Squamish Chief, Woodfibre issues Notice to Proceed (Apr 2022): https://www.squamishchief.com/local-news/wlng-says-it-has-given-the-final-green-light-for-construction-5283923 | Enbridge Woodfibre LNG project page: https://www.enbridge.com/projects-and-infrastructure/projects/woodfibre-lng | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | BC Hydro Woodfibre LNG interconnection: https://www.bchydro.com/energy-in-bc/projects/woodfibrelng.html | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki Woodfibre LNG Terminal: https://www.gem.wiki/Woodfibre_LNG_Terminal | LNG Journal, Woodfibre on track to complete construction by late 2027 (16 Jul 2026): https://lngjournal.com/index.php/latest-news-mainmenu-47/item/116798-woodfibre-lng-on-track-to-complete-construction-by-late-2027 | Woodfibre LNG, construction: https://woodfibrelng.ca/construction/ | Energetic City, export licence extension for Woodfibre LNG (29 Aug 2025): https://energeticcity.ca/2025/08/29/export-licence-extension-for-woodfibre-lng-granted-by-energy-regulator/ | Invest in Canada, Canada Investment Summit Prospectus (Sep 2026): https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3104,7 +3335,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Referred to Major Projects Office Sep 2025; designated national interest; FID targeted 2026.</t>
+          <t>Referred to the Major Projects Office Sep 2025 and designated national interest. Canada, British Columbia and LNG Canada agreed enhanced investment co-operation on 14 May 2026, targeting a 2026 FID. LNG Canada issued a limited notice to proceed to the JGC-Fluor joint venture in June 2026. Reuters reported on 24 Sep 2026 that an FID could come as early as October, and LNG Canada hopes to decide before the end of 2026. No FID as of 27 Sep 2026, so the tier stays advanced_proposed.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3134,7 +3365,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N11" t="b">
@@ -3279,7 +3510,7 @@
       </c>
       <c r="BB11" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Major Projects Office, LNG Canada Phase 2: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki: https://www.gem.wiki/LNG_Canada_Terminal</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Major Projects Office, LNG Canada Phase 2: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki: https://www.gem.wiki/LNG_Canada_Terminal | The Northern View, Phase 2 decision could come as early as October (24 Sep 2026): https://thenorthernview.com/2026/09/24/lng-canada-phase-2-decision-could-come-as-early-as-october/</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3326,7 +3557,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Environmental approvals Sep 2025; referred to Major Projects Office Nov 2025; FID targeted 2026.</t>
+          <t>Environmental approvals 15 Sep 2025; referred to the Major Projects Office 13 Nov 2025. Offtake agreements now cover about 8 of 12 mtpa (Shell, TotalEnergies, SEFE, Uniper, Santos). First deliveries expected in 2032 under the Uniper agreement. No FID as of 27 Sep 2026.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3351,14 +3582,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N12" t="b">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
@@ -3401,19 +3632,19 @@
         <v>3800</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
-          <t>Shell plc; TotalEnergies SE (2 mtpa)</t>
+          <t>Shell plc (2 mtpa); TotalEnergies SE (2 mtpa); Uniper SE (2 mtpa); SEFE (1 mtpa); Santos (1 mtpa)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20 years (TotalEnergies)</t>
+          <t>20 years (TotalEnergies, Santos); up to 20 years (SEFE, Uniper)</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr"/>
@@ -3457,7 +3688,7 @@
       </c>
       <c r="AN12" s="4" t="inlineStr">
         <is>
-          <t>MOU signed 20 Jan 2026 for up to 600 MW, conditional on North Coast Transmission Line expansion</t>
+          <t>MOU with BC Hydro signed 20 Jan 2026 for up to 600 MW over a ~120 km Nass Valley Regional Transmission Line, conditional on the North Coast Transmission Line (NCTL) expansion. NCTL phase 2, west toward Terrace, starts construction in 2027 and is due to be complete by winter 2032.</t>
         </is>
       </c>
       <c r="AO12" s="4" t="inlineStr">
@@ -3473,7 +3704,7 @@
       </c>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>GL-346, 40 year term, issued 15 Mar 2023</t>
+          <t>GL-346, 40 year term, issued 15 Mar 2023. Early-expiry clause: the term ends 10 years after issuance if LNG exports have not begun, so exports must start by about March 2033. First deliveries are now expected in 2032.</t>
         </is>
       </c>
       <c r="AT12" t="n">
@@ -3516,7 +3747,7 @@
       </c>
       <c r="BB12" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Major Projects Office, Ksi Lisims LNG: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html | BC Government news release 2026ECS0002: https://news.gov.bc.ca/releases/2026ECS0002-000043 | NGI, Ksi Lisims power agreement: https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/ | TotalEnergies offtake release: https://www.businesswire.com/news/home/20250519012495/en/ | GEM wiki: https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Major Projects Office, Ksi Lisims LNG: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html | BC Government news release 2026ECS0002: https://news.gov.bc.ca/releases/2026ECS0002-000043 | NGI, Ksi Lisims power agreement: https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/ | TotalEnergies offtake release: https://www.businesswire.com/news/home/20250519012495/en/ | GEM wiki: https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal | BC Government, Ksi Lisims and SEFE agreement (27 May 2026): https://news.gov.bc.ca/releases/2026ECS0025-000604 | NRCan, third international offtake deal (15 Sep 2026): https://www.canada.ca/en/natural-resources-canada/news/2026/09/canadian-lng-project-signs-third-international-offtake-deal.html | BC Government, North Coast Transmission Line: https://news.gov.bc.ca/releases/2026PREM0034-001026</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -3538,6 +3769,9 @@
         <is>
           <t>2026-08-28</t>
         </is>
+      </c>
+      <c r="BG12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3573,7 +3807,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>On federal export project list under a 25 year export licence; BC EAO approval expected 2026.</t>
+          <t>BC environmental assessment certificate and federal decision statement both issued 21 Sep 2026 through a substituted assessment. Certified for up to 7,700 tonnes a day of new liquefaction and a 142,400 m3 tank, at about C$3.1bn with a six-year build. No FID. On the federal export project list under a 25 year export licence.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3598,7 +3832,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N13" t="b">
@@ -3614,7 +3848,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>GEM records Phase 2 as a 2.5 mtpa addition. Local reporting (May 2026) states Phase 2 brings TOTAL site production to 2.5 mtpa, implying an addition of about 1.6. LNG Prime cites an 'up to about 2.6 mtpa' liquefaction component. Unresolved; GEM's 2.5 retained.</t>
+          <t>GEM records Phase 2 as a 2.5 mtpa addition. The environmental assessment certificate (21 Sep 2026) covers up to 7,700 tonnes a day of new liquefaction, 2.8 Mt a year at 365 days, so 2.5 mtpa is consistent with an addition rather than a site total. The earlier local reading of an addition of about 1.6 is set aside. GEM's 2.5 retained.</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
@@ -3713,7 +3947,7 @@
       <c r="BA13" s="4" t="inlineStr"/>
       <c r="BB13" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki: https://www.gem.wiki/Tilbury_Island_LNG_Terminal</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki: https://www.gem.wiki/Tilbury_Island_LNG_Terminal | Impact Assessment Agency of Canada, Tilbury Phase 2 decision (21 Sep 2026): https://www.canada.ca/en/impact-assessment-agency/news/2026/09/major-milestone-completed.html | Surrey Now-Leader, Tilbury Phase 2 EA certificate (21 Sep 2026): https://surreynowleader.com/2026/09/21/delta-lng-expansion-project-issued-b-c-environmental-assessment-certificate/</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3984,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Proposed expansion. Not listed as a separate export project by NRCan; primarily marine bunkering and domestic supply.</t>
+          <t>Proposed expansion, primarily marine bunkering and domestic supply; not listed separately by NRCan. An Order in Council of 24 Jul 2026 exempts it from needing a Certificate of Public Convenience and Necessity. More than C$2bn, construction from mid-2027, in service as early as 2031, with an equity option for the Musqueam Indian Band.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3775,14 +4009,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
@@ -3889,8 +4123,11 @@
       <c r="BA14" s="4" t="inlineStr"/>
       <c r="BB14" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | GEM wiki: https://www.gem.wiki/Tilbury_Island_LNG_Terminal</t>
-        </is>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | GEM wiki: https://www.gem.wiki/Tilbury_Island_LNG_Terminal | BC Government, Tilbury Phase 1B Order in Council (24 Jul 2026): https://news.gov.bc.ca/releases/2026ECS0043-000870</t>
+        </is>
+      </c>
+      <c r="BG14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3929,7 +4166,16 @@
           <t>Tilbury Island, Delta</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Tilbury Jetty Limited Partnership (affiliate of FortisBC Holdings Inc.)</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>FortisBC Holdings Inc. (via Tilbury Jetty Limited Partnership)</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>proposed</t>
@@ -3937,7 +4183,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N15" t="b">
@@ -3962,7 +4208,11 @@
       <c r="W15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="inlineStr"/>
       <c r="AC15" s="4" t="inlineStr"/>
-      <c r="AE15" s="4" t="inlineStr"/>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>Now named the Tilbury Pacific Marine Jetty Project. Would supply LNG to bunkering vessels in the Port of Vancouver. No service date announced.</t>
+        </is>
+      </c>
       <c r="AF15" t="inlineStr">
         <is>
           <t>export infrastructure (marine jetty)</t>
@@ -4007,7 +4257,7 @@
       <c r="BA15" s="4" t="inlineStr"/>
       <c r="BB15" s="4" t="inlineStr">
         <is>
-          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | CER Export Licence Applications schedule: https://www.cer-rec.gc.ca/en/applications-hearings/view-applications-projects/export-licence-applications/</t>
+          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | CER Export Licence Applications schedule: https://www.cer-rec.gc.ca/en/applications-hearings/view-applications-projects/export-licence-applications/ | Tilbury Pacific Marine Jetty, About: https://tilburypacific.ca/about-tilbury-pacific/</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4284,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Early-stage proposal. The 17 August 2026 release states that no formal regulatory process has yet begun. No initial project description has been filed with the Impact Assessment Agency. The feedgas pipeline from Western Canada is described only as a combination of existing and new infrastructure; the route is undefined.</t>
+          <t>Early-stage proposal. The 17 August 2026 release states that no formal regulatory process has yet begun. No initial project description has been filed with the Impact Assessment Agency. The feedgas pipeline from Western Canada is described only as a combination of existing and new infrastructure; the route is undefined. Listed as 'Pre-Application' in the federal Canada Investment Summit Prospectus (Sep 2026).</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4064,7 +4314,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N16" t="b">
@@ -4109,7 +4359,7 @@
       <c r="AC16" s="4" t="inlineStr"/>
       <c r="AE16" s="4" t="inlineStr">
         <is>
-          <t>No regulatory process has begun. The pipeline route from Western Canada to Baie-Comeau is undefined. The release claims renewable electricity in Quebec; electric drive is not assumed.</t>
+          <t>No regulatory process has begun; the federal prospectus lists the project at 'Pre-Application' with a capital cost of US$23B (Sep 2026), while Radio-Canada reporting cites about C$30bn. Kino Aski Inc. (Atikamekw-led) holds the majority and Marinvest Energy Canada a minority. Naftogaz signed a memorandum of understanding on 11 Sep 2026 to assess buying Canadian LNG. The Anishnabe Nation of Lac-Simon says the project lacks community consent. Electric drive is claimed but not assumed.</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -4132,7 +4382,7 @@
       </c>
       <c r="AJ16" s="4" t="inlineStr">
         <is>
-          <t>previously classified as electric_planned. Company reported to be planning its own wind farm. No filed plan.</t>
+          <t>previously classified as electric_planned. The developer plans up to three electric-drive FLNG units powered by about 1,700 MW of planned wind capacity. No contracted supply and no filed plan; electric drive is not assumed.</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4157,7 +4407,7 @@
       </c>
       <c r="AO16" s="4" t="inlineStr">
         <is>
-          <t>Aspirational - 17 August 2026 release claims renewable power; no contracted supply. Electric drive is not assumed.</t>
+          <t>Aspirational - about 1,700 MW of planned wind for up to three electric-drive FLNG units; no contracted supply. Electric drive is not assumed.</t>
         </is>
       </c>
       <c r="AS16" s="4" t="inlineStr">
@@ -4185,17 +4435,17 @@
       <c r="BA16" s="4" t="inlineStr"/>
       <c r="BB16" s="4" t="inlineStr">
         <is>
-          <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html | The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ | Greenpeace Canada, Marinvest: https://www.greenpeace.org/canada/en/story/75493/marinvest-the-biggest-lng-project-youve-never-heard-of/ | CBC: https://www.cbc.ca/news/canada/montreal/quebec-lng-baie-comeau-1.7648993 | National Observer: https://www.nationalobserver.com/2026/02/20/news/marinvest-quebec-lng-project-ottawa</t>
+          <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html | The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ | Greenpeace Canada, Marinvest: https://www.greenpeace.org/canada/en/story/75493/marinvest-the-biggest-lng-project-youve-never-heard-of/ | CBC: https://www.cbc.ca/news/canada/montreal/quebec-lng-baie-comeau-1.7648993 | National Observer: https://www.nationalobserver.com/2026/02/20/news/marinvest-quebec-lng-project-ottawa | Kino Aski LNG website: https://kinoaskilng.ca/ | gasworld, Kino Aski LNG targets North America-Europe energy corridor: https://www.gasworld.com/story/kino-aski-lng-targets-north-america-europe-energy-corridor/2257622.article/ | Invest in Canada, Canada Investment Summit Prospectus (Sep 2026): https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf | The Energy Mix, Kino Aski signs tentative deal with Naftogaz (16 Sep 2026): https://www.theenergymix.com/kino-aski-lng-signs-tentative-deal-with-ukraine-state-fossil-as-opposition-rises-complications-abound/ | Québec Nouvelles, third route studied (Sep 2026): https://www.quebecnouvelles.com/un-troisieme-trace-etudie-pour-livrer-du-gnl-a-baie-comeau-1441870.html</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>not available</t>
+          <t>Western Canada Sedimentary Basin (developer-stated; producing area not named)</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>The feedgas route is undefined. The two candidate supplies are Western Canadian gas reaching the Quebec north shore via the TC Energy Canadian Mainline, and United States Appalachian gas. Neither is stated by the proponent. This distinction is the subject of the Kino Aski feedgas sensitivity, because it decides both the pipeline transport distance and whether upstream and pipeline emissions are Canada territorial or foreign.</t>
+          <t>The developer now names Western Canadian gas, carried over existing networks plus about 1,000 km of new pipeline to Baie-Comeau. The route is still undefined: three corridors are under study, including a new central route through Atikamekw Nitaskinan territory. No source names US supply, so the US Appalachian case in the Kino Aski feedgas sensitivity no longer has a basis (code change pending).</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4670,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Proposed floating LNG. MOU with Hanwha Ocean Jan 2026. No capacity disclosed. Approved marine base only, no LNG plant proposal filed.</t>
+          <t>Proposed floating LNG at the Fermeuse Marine Base. MOU with Hanwha Ocean Jan 2026. The developer has stated up to 10 mtpa (Mar 2026) but has filed no LNG plant proposal; only the marine base is approved.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -4450,7 +4700,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -4458,11 +4708,11 @@
       </c>
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>Derived, not published, and conditional on the proponent's own resource claim. The proponent has not stated a liquefaction capacity. Fermeuse Energy states the project would develop 9.7 trillion cubic feet of offshore associated gas in the Jeanne d'Arc Basin, which is 275 billion cubic metres. DERIVATION: 275 bcm / 1.38 bcm per mtpa (lng_to_gas_bcm_per_mtpa, the gas-equivalent of LNG OUTPUT) / 40 years = 4.98 mtpa of output if every molecule became LNG. It does not: liquefaction burns part of the throughput as fuel. Using the model's own factors so the derivation is internally consistent, the liquefaction stage emits 0.29 tCO2e per t LNG and burning gas releases 2.75 tCO2 per t (combustion central), so fuel is 0.29 / 2.75 = 0.1055 t per t LNG and feedgas per tonne of LNG is 1.1055 t. Output is therefore 4.98 / 1.1055 = 4.51, recorded as 4.5 mtpa. That treats the whole liquefaction factor as fuel combustion; the small non-combustion part (flaring, venting) makes the fuel share slightly high and the capacity slightly low, inside the rounding. WHAT PUSHES THIS FIGURE UP, and why it is not a lower bound: it assumes (a) 100 per cent recovery of a resource stated by the proponent, not a regulator or an independent estimate; (b) a flat 40-year production profile, whereas associated gas follows the oil decline and would front-load output; and (c) no reservation of gas for platform fuel, reinjection or domestic supply. Each choice raises the capacity, so the figure is closer to an upper bound on the proponent's claim than to a conservative one. Two other approaches give higher figures and were not used: the same resource over a 25-year life gives about 8 mtpa net of fuel, and benchmarking the stated US$12 to 15 billion capital cost against Ksi Lisims and Cedar gives 9 to 12 mtpa. An unsourced third-party table circulates a figure of 10 mtpa. HISTORY: 5.0 mtpa until 3 September 2026, from the same resource without netting the fuel share, and described as 'the lowest defensible derivation', which it was not.</t>
+          <t>Developer statement: up to 10 mtpa, from Crown LNG's chief executive in The Narwhal (19 Mar 2026). No project description or LNG plant application has been filed; only the marine base is approved. Feedgas would come through a 380 km subsea pipeline from the Jeanne d'Arc Basin (same source). HISTORY: 4.5 mtpa from 3 to 27 Sep 2026 and 5.0 mtpa before that, both derived from the developer's 9.7 Tcf resource over a 40-year life because no stated capacity had been found. That derivation is superseded; the resource claim now sets the operating life instead (see project_life_years).</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr">
@@ -4524,6 +4774,9 @@
       <c r="AM18" s="4" t="inlineStr"/>
       <c r="AN18" s="4" t="inlineStr"/>
       <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>18</v>
+      </c>
       <c r="AS18" s="4" t="inlineStr"/>
       <c r="AU18" t="inlineStr">
         <is>
@@ -4546,7 +4799,7 @@
       <c r="BA18" s="4" t="inlineStr"/>
       <c r="BB18" s="4" t="inlineStr">
         <is>
-          <t>Fermeuse Energy news release, 2 September 2025 | GEM Fermeuse Energy FLNG Terminal, https://www.gem.wiki/Fermeuse_Energy_FLNG_Terminal | CBC, 10 February 2026, https://www.cbc.ca/news/canada/newfoundland-labrador/fermeuse-lng-proposed-project-9.7082941 | GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NGI, Eastern Canada LNG / Hanwha: https://naturalgasintel.com/news/eastern-canada-lng-back-in-focus-as-hanwha-enters-newfoundland-project/</t>
+          <t>Fermeuse Energy news release, 2 September 2025 | GEM Fermeuse Energy FLNG Terminal, https://www.gem.wiki/Fermeuse_Energy_FLNG_Terminal | CBC, 10 February 2026, https://www.cbc.ca/news/canada/newfoundland-labrador/fermeuse-lng-proposed-project-9.7082941 | GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NGI, Eastern Canada LNG / Hanwha: https://naturalgasintel.com/news/eastern-canada-lng-back-in-focus-as-hanwha-enters-newfoundland-project/ | The Narwhal, LNG in Newfoundland: lessons from Kitimat (19 Mar 2026): https://thenarwhal.ca/lng-newfoundland-lessons-kitimat-bc/</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -4628,7 +4881,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4640,7 +4893,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>nameplate (GEM)</t>
+          <t>nameplate (GEM): 7.5 mtpa of import (regasification) capacity. NRCan's LNG project list gives 6.5 mtpa (page modified 7 Jan 2025). Conflict recorded, not resolved; the model uses terminal-specific throughput for this asset, so the figure barely affects results.</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
@@ -4706,7 +4959,7 @@
       <c r="BA19" s="4" t="inlineStr"/>
       <c r="BB19" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Saint_John_LNG_Terminal | Argus, New Brunswick restarts Saint John LNG talks: https://www.argusmedia.com/en/news-and-insights/latest-market-news/2727331-canada-s-new-brunswick-restarts-saint-john-lng-talks</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Saint_John_LNG_Terminal | Argus, New Brunswick restarts Saint John LNG talks: https://www.argusmedia.com/en/news-and-insights/latest-market-news/2727331-canada-s-new-brunswick-restarts-saint-john-lng-talks | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
     </row>
@@ -5487,38 +5740,38 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Cancelled 2021 per GEM.</t>
+          <t>Chevron and Woodside's Kitimat LNG was cancelled (GEM, 2021). In October 2025 yáqʷa Development Corporation, owned by the Haisla Nation, acquired from Chevron 'all relevant permits and licenses associated with Kitimat LNG, including Environmental Assessment Certificate, Export Licenses', with site remediation funding. The BC EAO lists the project as 'Post Decision - Care &amp; Maintenance'. No development plan, capacity or partner has been announced. Moved from inactive to watch on 27 Sep 2026: a fully permitted site with no live proposal. Capacity is the cancelled project's GEM figure and enters no total.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Chevron Canada</t>
+          <t>KM LNG Operating General Partnership (Bish LNG GP Ltd.)</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Chevron Corp [50.0%]; Woodside Energy Group Ltd [50.0%]</t>
+          <t>yáqʷa Development Corporation (Haisla Nation), acquired from Chevron Canada October 2025</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>shelved</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N26" t="b">
@@ -5529,7 +5782,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>Export licences transferred to yáqʷa with the site (October 2025); licence numbers and terms not verified.</t>
+        </is>
+      </c>
       <c r="R26" t="n">
         <v>18</v>
       </c>
@@ -5554,6 +5811,11 @@
         </is>
       </c>
       <c r="AJ26" s="4" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
       <c r="AL26" s="4" t="inlineStr"/>
       <c r="AM26" s="4" t="inlineStr"/>
       <c r="AN26" s="4" t="inlineStr"/>
@@ -5580,7 +5842,7 @@
       <c r="BA26" s="4" t="inlineStr"/>
       <c r="BB26" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Kitimat_LNG_Terminal</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Kitimat_LNG_Terminal | yáqʷa Development Corporation, acquisition of Kitimat LNG assets (17 Nov 2025): https://www.yaqwadevcorp.com/2025/11/18/yaq%CA%B7a-acquisition/ | BC EAO project record, Kitimat LNG (EPIC): https://projects.eao.gov.bc.ca/api/public/search?dataset=Project&amp;keywords=Kitimat&amp;pageNum=0&amp;pageSize=100</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7733,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Shelved. Pre-FID.</t>
+          <t>Shelved. Pre-FID. Its provincial environmental assessment registration (no. 2177, LNG Newfoundland and Labrador Limited, 23 Nov 2021) is still listed as Active with no decision (NL registry, checked 27 Sep 2026).</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7484,6 +7746,11 @@
           <t>Arnold's Cove</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>LNG Newfoundland and Labrador Limited</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
           <t>LNG Newfoundland and Labrador Ltd</t>
@@ -7496,7 +7763,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N43" t="b">
@@ -7563,7 +7830,7 @@
       <c r="BA43" s="4" t="inlineStr"/>
       <c r="BB43" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Placentia_Bay_FLNG_Terminal</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Placentia_Bay_FLNG_Terminal | Newfoundland and Labrador environmental assessment projects list: https://www.gov.nl.ca/ecc/env-assessment/projects-list/</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9283,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Announced 16 June 2026 via a non-binding memorandum of understanding between Kanata Clean Power and Hanwha Ocean. Estimated capital cost US$15.7 billion. No regulatory filing has been made and the gas transport route is described only as being from northeast British Columbia by unspecified means.</t>
+          <t>Announced 16 June 2026 via a non-binding MOU between Kanata Clean Power and Hanwha Ocean; estimated capital cost US$15.7 billion. On 14 Sep 2026 the parties agreed indicative terms: Hanwha Ocean's Energy Plant Unit would build, own and operate the facility as strategic partner and investor. A pre-FEED study follows a definitive agreement, full FEED is planned for 2027 and FID is targeted for early 2028. Final site selection is expected in Q4 2026. No regulatory filing has been made and the gas transport route is unspecified.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9036,7 +9303,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Kanata Clean Power; Hanwha Ocean (non-binding MOU); up to 50% offered to participating First Nations</t>
+          <t>Kanata Clean Power; Hanwha Ocean Energy Plant Unit (indicative terms, Sep 2026); a First Nation in the Prince Rupert region holds an exclusive right to acquire a 50/50 joint venture interest</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -9046,7 +9313,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9144,7 +9411,7 @@
       <c r="BA57" s="4" t="n"/>
       <c r="BB57" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html | Energy Intelligence, 18 June 2026, https://www.energyintel.com/0000019e-d707-d1c7-a9bf-ff5fb8d50000</t>
+          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html | Energy Intelligence, 18 June 2026, https://www.energyintel.com/0000019e-d707-d1c7-a9bf-ff5fb8d50000 | LNG Industry, Kanata and Hanwha Ocean to launch pre-FEED (14 Sep 2026): https://www.lngindustry.com/floating-lng/14092026/kanata-clean-power-and-hanwha-ocean-to-launch-pre-feed-for-proposed-floating-lng-project/</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -9155,6 +9422,596 @@
       <c r="BD57" t="inlineStr">
         <is>
           <t>Prince Rupert, British Columbia. The project is at memorandum of understanding stage and no feedgas route or supply basin has been stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>northern_prince_lng</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Not a live export proposal: no filed project description or environmental assessment, no named buyer and no named site. The developer's website claims heads of agreement for 6 mtpa on 'our larger project' and an 'initial LNG Export Permit'; the only CER records located are applications for short-term natural gas export orders and Order GO-116-2022, which authorise no facility or long-term volume. NeeStaNan places the 6 mtpa facility near Summit Lake, BC, the same area and containerised-rail concept as Summit Lake PG LNG, so the two may overlap. Watch rows enter no total.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Near Summit Lake, north of Prince George (per NeeStaNan); the developer names no site</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG Inc.</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Not disclosed ('Canadian Federally incorporated Company')</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>Short-term export order GO-116-2022 (term and volume not verified); no long-term GL licence located</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>6</v>
+      </c>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>Developer claim: heads of agreement for 6 mtpa on 'our larger project'; counterparties not named; no filed figure. Watch row, so it enters no total.</t>
+        </is>
+      </c>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>overseas export</t>
+        </is>
+      </c>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="4" t="inlineStr">
+        <is>
+          <t>Export project.</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Asia and Europe</t>
+        </is>
+      </c>
+      <c r="Y58" s="4" t="inlineStr">
+        <is>
+          <t>Containerised LNG by rail or truck to the coast (BOE Report, Mar 2024); port not named</t>
+        </is>
+      </c>
+      <c r="AC58" s="4" t="n"/>
+      <c r="AE58" s="4" t="inlineStr">
+        <is>
+          <t>MOU with NeeStaNan (Fox Lake Cree Nation) to assess a mid-scale LNG production and export operation at a Hudson Bay port; BOE Report dates it March 2024, a July 2025 release gives 8 Feb 2025. The website also mentions 'the first of a number of small-scale projects'.</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>export (not specified)</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>not_published</t>
+        </is>
+      </c>
+      <c r="AJ58" s="4" t="inlineStr">
+        <is>
+          <t>Drive type not published.</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="AL58" s="4" t="inlineStr">
+        <is>
+          <t>Assigned from end_use. Watch row: excluded from all totals.</t>
+        </is>
+      </c>
+      <c r="AM58" s="4" t="n"/>
+      <c r="AN58" s="4" t="n"/>
+      <c r="AO58" s="4" t="n"/>
+      <c r="AS58" s="4" t="inlineStr">
+        <is>
+          <t>Short-term order only; no long-term licence.</t>
+        </is>
+      </c>
+      <c r="AV58" s="4" t="n"/>
+      <c r="AW58" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AX58" s="4" t="n"/>
+      <c r="AY58" s="4" t="inlineStr">
+        <is>
+          <t>GO-116-2022 (short-term order)</t>
+        </is>
+      </c>
+      <c r="AZ58" s="4" t="inlineStr">
+        <is>
+          <t>https://apps.cer-rec.gc.ca/REGDOCS/Item/View/4459935</t>
+        </is>
+      </c>
+      <c r="BA58" s="4" t="n"/>
+      <c r="BB58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about | NeeStaNan, NeeStaNan and LNG Exports: https://neestanan.ca/neestanan-and-lng-exports/ | BOE Report, NeeStaNan signs MOU with Northern Prince LNG (5 Mar 2024): https://boereport.com/2024/03/05/neestanan-signs-mou-with-northern-prince-lng/ | BOE Report, NeeStaNan and Fox Lake Cree Nation secure federal authorization (2 Jul 2025): https://boereport.com/2025/07/02/neestanan-and-fox-lake-cree-nation-secure-federal-authorization-to-export-lng/ | CER REGDOCS, Northern Prince LNG Inc.: https://apps.cer-rec.gc.ca/REGDOCS/Item/View/4459935</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>hudson_bay_churchill_lng</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Port of Churchill Plus LNG (floating LNG concept)</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Government concept with no developer and no capacity. Port of Churchill Plus was referred to the Major Projects Office on 11 Sep 2025 as a transformative strategy; the MPO page (modified 21 May 2026) does not mention LNG. The federal Canada Investment Summit Prospectus (Sep 2026, p. 40) lists an 'LNG export corridor' with US$57B capex at the planning, engineering and feasibility stage. Manitoba's premier costs a version with a floating offshore LNG platform at $70 to 80 billion (CBC, 15 Sep 2026); Manitoba's sales tax exemption announced 14 Sep 2026 covers 'liquefied natural gas facilities'; Ottawa wants LNG shipped by 2030. The port is ice-bound outside late July to early November.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Port of Churchill, Hudson Bay (offshore floating platform concept)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>None named; promoted by the Government of Manitoba</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4" t="n"/>
+      <c r="S59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>overseas export</t>
+        </is>
+      </c>
+      <c r="U59" s="4" t="n"/>
+      <c r="W59" s="4" t="n"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="Y59" s="4" t="n"/>
+      <c r="AC59" s="4" t="n"/>
+      <c r="AE59" s="4" t="inlineStr">
+        <is>
+          <t>Federal target: LNG shipments by 2030, or federal backing is at risk (Global News, 17 Apr 2026).</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>export, floating (concept)</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>not_published</t>
+        </is>
+      </c>
+      <c r="AJ59" s="4" t="inlineStr">
+        <is>
+          <t>Drive type not published.</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="AL59" s="4" t="inlineStr">
+        <is>
+          <t>Assigned from end_use. Watch row: excluded from all totals.</t>
+        </is>
+      </c>
+      <c r="AM59" s="4" t="n"/>
+      <c r="AN59" s="4" t="n"/>
+      <c r="AO59" s="4" t="n"/>
+      <c r="AS59" s="4" t="inlineStr">
+        <is>
+          <t>No export licence identified.</t>
+        </is>
+      </c>
+      <c r="AV59" s="4" t="n"/>
+      <c r="AW59" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AX59" s="4" t="n"/>
+      <c r="AY59" s="4" t="n"/>
+      <c r="AZ59" s="4" t="n"/>
+      <c r="BA59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/en/privy-council/major-projects-office/projects/other/referred/churchill-plus.html</t>
+        </is>
+      </c>
+      <c r="BB59" s="4" t="inlineStr">
+        <is>
+          <t>Major Projects Office, Port of Churchill Plus: https://www.canada.ca/en/privy-council/major-projects-office/projects/other/referred/churchill-plus.html | Invest in Canada, Canada Investment Summit Prospectus (Sep 2026), p. 40: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf | CBC via Yahoo, Port of Churchill cost (15 Sep 2026): https://ca.news.yahoo.com/port-churchill-railway-improvements-cost-100000703.html | The Deep Dive, Manitoba PST exemption (15 Sep 2026): https://thedeepdive.ca/manitoba-pitches-pst-exemption-to-drive-port-of-churchill-investment/ | Global News, federal timeline for Port of Churchill (17 Apr 2026): https://globalnews.ca/news/11806964/federal-government-puts-timeline-in-place-for-port-of-churchill-project-kinew/</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>neestanan_port_nelson_lng</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NeeStaNan Port Nelson LNG export (feasibility)</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Feasibility study for a multi-commodity port at Port Nelson that would include LNG. The CER authorised NeeStaNan to export LNG until June 2027 so it can carry out the study (announced 2 Jul 2025). No capacity, facility filing or environmental assessment. Manitoba's premier: 'We haven't actually done an announcement of this thing yet.' MOU with Northern Prince LNG.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Proposed Port Nelson at the mouth of the Nelson River, Hudson Bay; planned 150 km rail spur from Gillam</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>NeeStaNan</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>NeeStaNan; majority owner Fox Lake Cree Nation</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>Short-term CER export authorisation to June 2027, for a feasibility study (order number and volume not verified)</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>overseas export</t>
+        </is>
+      </c>
+      <c r="U60" s="4" t="n"/>
+      <c r="W60" s="4" t="n"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="Y60" s="4" t="n"/>
+      <c r="AC60" s="4" t="n"/>
+      <c r="AE60" s="4" t="inlineStr">
+        <is>
+          <t>MOU with Northern Prince LNG to assess a mid-scale LNG production and export operation (BOE Report).</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>multi-commodity port including LNG (concept)</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>not_published</t>
+        </is>
+      </c>
+      <c r="AJ60" s="4" t="inlineStr">
+        <is>
+          <t>Drive type not published.</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="AL60" s="4" t="inlineStr">
+        <is>
+          <t>Assigned from end_use. Watch row: excluded from all totals.</t>
+        </is>
+      </c>
+      <c r="AM60" s="4" t="n"/>
+      <c r="AN60" s="4" t="n"/>
+      <c r="AO60" s="4" t="n"/>
+      <c r="AS60" s="4" t="inlineStr">
+        <is>
+          <t>Short-term authorisation to June 2027 only.</t>
+        </is>
+      </c>
+      <c r="AV60" s="4" t="n"/>
+      <c r="AW60" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AX60" s="4" t="n"/>
+      <c r="AY60" s="4" t="n"/>
+      <c r="AZ60" s="4" t="n"/>
+      <c r="BA60" s="4" t="n"/>
+      <c r="BB60" s="4" t="inlineStr">
+        <is>
+          <t>CBC, CER authorises NeeStaNan LNG exports: https://www.cbc.ca/1.7582120 | BOE Report, NeeStaNan and Fox Lake Cree Nation secure federal authorization (2 Jul 2025): https://boereport.com/2025/07/02/neestanan-and-fox-lake-cree-nation-secure-federal-authorization-to-export-lng/ | NeeStaNan, NeeStaNan and LNG Exports: https://neestanan.ca/neestanan-and-lng-exports/</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>project_northern_lights_lng</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Project Northern Lights (Cool LNG)</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>advanced_proposed</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Shovel-ready small-scale LNG plant, the first commercial deployment of Cool LNG's MA3 liquefaction technology: land and gas supply secured, engineering, zoning and subdivision completed and 'all required permits obtained'. Stage 1 capex US$60M, US$250M for stages 1 to 5; seeking equity, strategic partners and long-term offtake. No capacity or site published, so it enters no total.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Alberta (site not published)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Cool LNG (contact at Cool Ventures Inc.)</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable - domestic facility</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>Not available - the prospectus gives cost but no capacity</t>
+        </is>
+      </c>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>domestic supply (industrial, mining, remote communities, transport, utilities)</t>
+        </is>
+      </c>
+      <c r="U61" s="4" t="inlineStr">
+        <is>
+          <t>Markets across Western Canada.</t>
+        </is>
+      </c>
+      <c r="W61" s="4" t="inlineStr">
+        <is>
+          <t>Small-scale domestic supply; capacity not published.</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="Y61" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AC61" s="4" t="n"/>
+      <c r="AE61" s="4" t="n"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>small-scale liquefaction</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>not_published</t>
+        </is>
+      </c>
+      <c r="AJ61" s="4" t="inlineStr">
+        <is>
+          <t>Drive type not published. Uses Cool LNG's proprietary MA3 liquefaction technology.</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="AL61" s="4" t="inlineStr">
+        <is>
+          <t>Assigned from end_use. Outside the headline export scope.</t>
+        </is>
+      </c>
+      <c r="AM61" s="4" t="n"/>
+      <c r="AN61" s="4" t="n"/>
+      <c r="AO61" s="4" t="n"/>
+      <c r="AS61" s="4" t="inlineStr">
+        <is>
+          <t>No export licence - domestic facility</t>
+        </is>
+      </c>
+      <c r="AV61" s="4" t="n"/>
+      <c r="AW61" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AX61" s="4" t="n"/>
+      <c r="AY61" s="4" t="n"/>
+      <c r="AZ61" s="4" t="n"/>
+      <c r="BA61" s="4" t="n"/>
+      <c r="BB61" s="4" t="inlineStr">
+        <is>
+          <t>Invest in Canada, Canada Investment Summit Prospectus (Sep 2026), p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
         </is>
       </c>
     </row>
@@ -9170,7 +10027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF57"/>
+  <dimension ref="A1:BG61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9227,6 +10084,8 @@
     <col width="60" customWidth="1" min="52" max="52"/>
     <col width="60" customWidth="1" min="53" max="53"/>
     <col width="60" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -9520,6 +10379,11 @@
           <t>gem_status_date</t>
         </is>
       </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>first_export_year_assumes_fid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9812,6 +10676,11 @@
           <t>GEM wiki, read 2026-08-28: https://www.gem.wiki/LNG_Canada_Terminal - status field quoted verbatim. gem_status_date is the page's last-modified date.</t>
         </is>
       </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10104,6 +10973,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10396,6 +11270,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10688,6 +11567,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10980,6 +11864,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11029,209 +11918,209 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>Cryopeak Energy Solutions website: https://www.cryopeak.com/ - current company name; 'owns and operates three advanced LNG production facilities throughout Western Canada'. NRCan listed the owner as Cryopeak LNG Solutions: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Cryopeak Energy Solutions website: https://www.cryopeak.com/ - current company name; 'owns and operates three advanced LNG production facilities throughout Western Canada'. NRCan listed the owner as Cryopeak LNG Solutions: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Date we last verified against the sources listed</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable - domestic facility</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Date we last verified against the sources listed</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable - domestic facility</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Derived: domestic facilities supply the domestic market</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>Derived: domestic facility</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Derived: domestic facilities supply the domestic market</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us from end_use</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>Not published for small plants</t>
+        </is>
+      </c>
+      <c r="AL7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>Derived: domestic facility</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AM7" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AP7" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AQ7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AR7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AS7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AT7" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AU7" s="4" t="inlineStr">
+        <is>
+          <t>Not available - absent from GEM GGIT LNG Terminals Sep 2025</t>
+        </is>
+      </c>
+      <c r="AV7" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AW7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
-        <is>
-          <t>Assigned by us from end_use</t>
-        </is>
-      </c>
-      <c r="AJ7" s="4" t="inlineStr">
-        <is>
-          <t>Compiled by us</t>
-        </is>
-      </c>
-      <c r="AK7" s="4" t="inlineStr">
-        <is>
-          <t>Not published for small plants</t>
-        </is>
-      </c>
-      <c r="AL7" s="4" t="inlineStr">
+      <c r="AX7" s="4" t="inlineStr">
         <is>
           <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
-      <c r="AM7" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AN7" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AO7" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AP7" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AQ7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AR7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AS7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AT7" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="AU7" s="4" t="inlineStr">
-        <is>
-          <t>Not available - absent from GEM GGIT LNG Terminals Sep 2025</t>
-        </is>
-      </c>
-      <c r="AV7" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
-        </is>
-      </c>
-      <c r="AX7" s="4" t="inlineStr">
-        <is>
-          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
-        </is>
-      </c>
       <c r="AY7" s="4" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -11270,6 +12159,11 @@
       <c r="BF7" t="inlineStr">
         <is>
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -11564,6 +12458,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11598,7 +12497,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Cedar_FLNG_Terminal</t>
+          <t>Cedar LNG spring 2026 newsletter: https://www.cedarlng.com/2026/04/30/spring-2026-newsletter/ | Pembina, 15 Dec 2025: https://www.pembina.com/media-centre/news/details/26400a51-ee23-4209-b789-4a15c2f699d1</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -11643,7 +12542,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ LatestPlannedStartYear=2028</t>
+          <t>Pembina, 15 Dec 2025: https://www.pembina.com/media-centre/news/details/26400a51-ee23-4209-b789-4a15c2f699d1 - 'expected in-service date in late 2028'. Cedar LNG spring 2026 newsletter: https://www.cedarlng.com/2026/04/30/spring-2026-newsletter/ - FLNG vessel more than 50% complete, scheduled for delivery to Kitimat in 2028. Consistent with GEM GGIT (Sep 2025) LatestPlannedStartYear=2028.</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -11653,12 +12552,12 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>Cedar LNG FID announcement (25 Jun 2024): https://www.cedarlng.com/cedar-lng-announces-positive-final-investment-decision/ - states nameplate capacity of 3.3 mtpa. Corroborated by GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ CapacityinMtpa=3.3. NRCan and CER both state 3.0, treated as licenced or rounded.</t>
+          <t>Cedar LNG application to amend its BC environmental assessment certificate (BC EAO, EPIC): https://projects.eao.gov.bc.ca/api/public/document/68caf0067a03b4002205daf9/download/Cedar%20LNG%20Accommodation%20+%20Capacity%20Amendment%20Application.pdf - liquefaction from 400 to 500 million standard cubic feet a day, from about 3.0 to 3.75 mtpa, through efficiencies realised in detailed design with no change to equipment. Amended certificate issued by the BC EAO in July 2026: Canadian Vanguard: https://www.thecanadianvanguard.com/cedar-lng-secures-bc-regulatory-nod-to-expand-future-output-capacity/ (9 Jul 2026); GIIGNL: https://www.giignl.org/news/cedar-lng-receives-approval-to-increase-project-capacity (22 Jul 2026), which notes the change remains subject to approvals under the Impact Assessment Act and from the BC Energy Regulator. Replaces 3.3 mtpa from the FID announcement (25 Jun 2024): https://www.cedarlng.com/cedar-lng-announces-positive-final-investment-decision/</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/</t>
+          <t>BC EAO amendment application: https://projects.eao.gov.bc.ca/api/public/document/68caf0067a03b4002205daf9/download/Cedar%20LNG%20Accommodation%20+%20Capacity%20Amendment%20Application.pdf | Canadian Vanguard: https://www.thecanadianvanguard.com/cedar-lng-secures-bc-regulatory-nod-to-expand-future-output-capacity/ | GIIGNL: https://www.giignl.org/news/cedar-lng-receives-approval-to-increase-project-capacity</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
@@ -11854,6 +12753,11 @@
       <c r="BF9" t="inlineStr">
         <is>
           <t>GEM wiki, read 2026-08-28: https://www.gem.wiki/Cedar_FLNG_Terminal - status field quoted verbatim. gem_status_date is the page's last-modified date.</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -11890,7 +12794,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Woodfibre_LNG_Terminal</t>
+          <t>LNG Journal, 16 Jul 2026: https://lngjournal.com/index.php/latest-news-mainmenu-47/item/116798-woodfibre-lng-on-track-to-complete-construction-by-late-2027 | GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Woodfibre_LNG_Terminal</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -11935,12 +12839,12 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ LatestPlannedStartYear=2028. NOTE: Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook and CER cite 2027</t>
+          <t>LNG Journal, 16 Jul 2026: https://lngjournal.com/index.php/latest-news-mainmenu-47/item/116798-woodfibre-lng-on-track-to-complete-construction-by-late-2027 - chief executive Luke Schauerte 'targets end-2027 for in-service'; project more than halfway complete. Woodfibre LNG construction page: https://woodfibrelng.ca/construction/ - 'substantial completion of the Project is expected by 2027'. Replaces 2028 from GEM GGIT (Sep 2025) under the 27 Sep 2026 rule that the developer's latest stated in-service year is used. An end-of-year start means little LNG in 2027 itself; the model's 40% first-year ramp overstates that year slightly.</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Energetic City, 29 Aug 2025: https://energeticcity.ca/2025/08/29/export-licence-extension-for-woodfibre-lng-granted-by-energy-regulator/</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -12010,34 +12914,34 @@
       </c>
       <c r="AE10" s="4" t="inlineStr">
         <is>
+          <t>Compiled by us | Canada Investment Summit Prospectus, p. 10: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="AF10" s="4" t="inlineStr">
+        <is>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ FacilityType</t>
+        </is>
+      </c>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ Floating</t>
+        </is>
+      </c>
+      <c r="AH10" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us from end_use, see chain_note</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
+        <is>
           <t>Compiled by us</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
-        <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ FacilityType</t>
-        </is>
-      </c>
-      <c r="AG10" s="4" t="inlineStr">
-        <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ Floating</t>
-        </is>
-      </c>
-      <c r="AH10" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr">
-        <is>
-          <t>Assigned by us from end_use, see chain_note</t>
-        </is>
-      </c>
-      <c r="AJ10" s="4" t="inlineStr">
-        <is>
-          <t>Compiled by us</t>
-        </is>
-      </c>
       <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>Assigned gas_turbine, August 2026 electrification revision; previous classification retained in liquefaction_drive_note</t>
@@ -12080,7 +12984,7 @@
       </c>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>40-year term from the licence filing. End year = licence_issued_year + authorised_export_term_years, conservative (term may run from first export instead).</t>
+          <t>40-year term from the licence filing. End year = licence_issued_year + authorised_export_term_years, conservative (term may run from first export instead). | Energetic City, 29 Aug 2025: https://energeticcity.ca/2025/08/29/export-licence-extension-for-woodfibre-lng-granted-by-energy-regulator/ (deadline extension)</t>
         </is>
       </c>
       <c r="AT10" s="4" t="inlineStr">
@@ -12146,6 +13050,11 @@
       <c r="BF10" t="inlineStr">
         <is>
           <t>GEM wiki, read 2026-08-28: https://www.gem.wiki/Woodfibre_LNG_Terminal - status field quoted verbatim. gem_status_date is the page's last-modified date.</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -12182,7 +13091,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Major Projects Office, LNG Canada Phase 2: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html</t>
+          <t>Major Projects Office, LNG Canada Phase 2 (modified 2 Jul 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html | GEM wiki, LNG Canada Terminal (edited 25 Sep 2026): https://www.gem.wiki/LNG_Canada_Terminal | The Northern View, 24 Sep 2026 (Reuters): https://thenorthernview.com/2026/09/24/lng-canada-phase-2-decision-could-come-as-early-as-october/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -12227,7 +13136,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ LatestPlannedStartYear=2030</t>
+          <t>GEM wiki, LNG Canada Terminal (edited 25 Sep 2026): https://www.gem.wiki/LNG_Canada_Terminal - planned first LNG for Phase 2 is 2030. Unchanged from GEM GGIT (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ LatestPlannedStartYear=2030. No developer date published; replace with the date given at FID.</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -12438,6 +13347,11 @@
       <c r="BF11" t="inlineStr">
         <is>
           <t>GEM wiki, read 2026-08-28: https://www.gem.wiki/LNG_Canada_Terminal - status field quoted verbatim. gem_status_date is the page's last-modified date.</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -12474,7 +13388,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal</t>
+          <t>Major Projects Office, Ksi Lisims LNG (modified 14 Sep 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html | NRCan, third international offtake deal (15 Sep 2026): https://www.canada.ca/en/natural-resources-canada/news/2026/09/canadian-lng-project-signs-third-international-offtake-deal.html | GEM wiki: https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -12519,7 +13433,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ LatestPlannedStartYear=2029</t>
+          <t>Major Projects Office, Ksi Lisims LNG (modified 14 Sep 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html - Uniper agreement of 29 Jul 2026, 'with first deliveries expected to begin 2032'. Corroborated by BC Government release of 27 May 2026 (SEFE agreement): https://news.gov.bc.ca/releases/2026ECS0025-000604 - 'deliveries expected to begin by the early 2030s'. Replaces 2029 from GEM GGIT (Sep 2025) LatestPlannedStartYear; GEM wiki still says 2029 at its 25 Sep 2026 edit: https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -12574,7 +13488,7 @@
       </c>
       <c r="AA12" s="4" t="inlineStr">
         <is>
-          <t>NGI, Ksi Lisims LNG power agreement: https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/; TotalEnergies offtake release (May 2025): https://www.businesswire.com/news/home/20250519012495/en/</t>
+          <t>Sum of five published agreements. Shell 2 mtpa: NGI, https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/ | TotalEnergies 2 mtpa, 20 years: https://www.businesswire.com/news/home/20250519012495/en/ | SEFE 1 mtpa, up to 20 years (27 May 2026): https://news.gov.bc.ca/releases/2026ECS0025-000604 | Uniper 2 mtpa, up to 20 years (29 Jul 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html | Santos 1 mtpa, 20 years (14 Sep 2026): https://www.canada.ca/en/natural-resources-canada/news/2026/09/canadian-lng-project-signs-third-international-offtake-deal.html</t>
         </is>
       </c>
       <c r="AB12" s="4" t="inlineStr">
@@ -12584,12 +13498,12 @@
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
-          <t>NGI, Ksi Lisims LNG power agreement: https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/; TotalEnergies offtake release (May 2025): https://www.businesswire.com/news/home/20250519012495/en/</t>
+          <t>Shell 2 mtpa: NGI, https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/ | TotalEnergies 2 mtpa, 20 years: https://www.businesswire.com/news/home/20250519012495/en/ | SEFE 1 mtpa, up to 20 years (27 May 2026): https://news.gov.bc.ca/releases/2026ECS0025-000604 | Uniper 2 mtpa, up to 20 years (29 Jul 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html | Santos 1 mtpa, 20 years (14 Sep 2026): https://www.canada.ca/en/natural-resources-canada/news/2026/09/canadian-lng-project-signs-third-international-offtake-deal.html</t>
         </is>
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>NGI, Ksi Lisims LNG power agreement: https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/; TotalEnergies offtake release (May 2025): https://www.businesswire.com/news/home/20250519012495/en/</t>
+          <t>Shell 2 mtpa: NGI, https://naturalgasintel.com/news/ksi-lisims-lng-power-agreement-advances-bcs-natural-gas-export-buildout/ | TotalEnergies 2 mtpa, 20 years: https://www.businesswire.com/news/home/20250519012495/en/ | SEFE 1 mtpa, up to 20 years (27 May 2026): https://news.gov.bc.ca/releases/2026ECS0025-000604 | Uniper 2 mtpa, up to 20 years (29 Jul 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html | Santos 1 mtpa, 20 years (14 Sep 2026): https://www.canada.ca/en/natural-resources-canada/news/2026/09/canadian-lng-project-signs-third-international-offtake-deal.html</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr">
@@ -12639,7 +13553,7 @@
       </c>
       <c r="AN12" s="4" t="inlineStr">
         <is>
-          <t>Major Projects Office, Ksi Lisims LNG: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html; BC Government news release 2026ECS0002: https://news.gov.bc.ca/releases/2026ECS0002-000043</t>
+          <t>Major Projects Office, Ksi Lisims LNG: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html (600 MW, Nass Valley line) | BC Government news release 2026ECS0002: https://news.gov.bc.ca/releases/2026ECS0002-000043 | BC Government, North Coast Transmission Line (Sep 2026): https://news.gov.bc.ca/releases/2026PREM0034-001026 (phase 2 complete by winter 2032)</t>
         </is>
       </c>
       <c r="AO12" s="4" t="inlineStr">
@@ -12664,7 +13578,7 @@
       </c>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>40-year term from the licence filing. End year = licence_issued_year + authorised_export_term_years, conservative (term may run from first export instead).</t>
+          <t>40-year term from the licence filing. End year = licence_issued_year + authorised_export_term_years, conservative (term may run from first export instead). | GEM wiki, Ksi Lisims FLNG Terminal (edited 25 Sep 2026): https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal - 'early expiration clause where the term of the license ends 10 years after the date of issuance' if exports have not commenced. Licence text not opened (CER REGDOCS unreachable, 26 Sep 2026).</t>
         </is>
       </c>
       <c r="AT12" s="4" t="inlineStr">
@@ -12730,6 +13644,11 @@
       <c r="BF12" t="inlineStr">
         <is>
           <t>GEM wiki, read 2026-08-28: https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal - status field quoted verbatim. gem_status_date is the page's last-modified date.</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Major Projects Office, Ksi Lisims LNG (modified 14 Sep 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/ksi-lisims.html - Uniper agreement of 29 Jul 2026, 'first deliveries expected to begin 2032'. GEM wiki: https://www.gem.wiki/Ksi_Lisims_FLNG_Terminal - FID 'expected in 2026'. The 2032 date is a developer delivery date that already allows for the build after a 2026 FID, so fid_delay_mid is not added on top (decision 27 Sep 2026).</t>
         </is>
       </c>
     </row>
@@ -12766,7 +13685,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects; Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook</t>
+          <t>Impact Assessment Agency of Canada, 21 Sep 2026: https://www.canada.ca/en/impact-assessment-agency/news/2026/09/major-milestone-completed.html | Surrey Now-Leader, 21 Sep 2026: https://surreynowleader.com/2026/09/21/delta-lng-expansion-project-issued-b-c-environmental-assessment-certificate/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -12826,7 +13745,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | Surrey Now-Leader, 21 Sep 2026: https://surreynowleader.com/2026/09/21/delta-lng-expansion-project-issued-b-c-environmental-assessment-certificate/</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
@@ -13022,6 +13941,11 @@
       <c r="BF13" t="inlineStr">
         <is>
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13982,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects; Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook</t>
+          <t>NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | BC Government news release 2026ECS0043: https://news.gov.bc.ca/releases/2026ECS0043-000870</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -13103,7 +14027,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ LatestPlannedStartYear=2028</t>
+          <t>BC Government news release 2026ECS0043 (Order in Council of 24 Jul 2026): https://news.gov.bc.ca/releases/2026ECS0043-000870 - construction 'as early as mid-2027', 'in service as early as 2031'. Replaces 2028 from GEM GGIT (Sep 2025).</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -13314,6 +14238,11 @@
       <c r="BF14" t="inlineStr">
         <is>
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>BC Government news release 2026ECS0043 (24 Jul 2026): https://news.gov.bc.ca/releases/2026ECS0043-000870 - construction 'as early as mid-2027', 'in service as early as 2031'. The 2031 date already includes the build period, so fid_delay_mid is not added on top (decision 27 Sep 2026).</t>
         </is>
       </c>
     </row>
@@ -13365,12 +14294,12 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Not available - NRCan names the project, not the proponent</t>
+          <t>Tilbury Pacific Marine Jetty, About: https://tilburypacific.ca/about-tilbury-pacific/ - 'Tilbury Jetty Limited Partnership is the proponent of the Tilbury Pacific Marine Jetty Project, an affiliate of FortisBC Holdings Inc.'</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Not available - NRCan names the project, not the proponent</t>
+          <t>Tilbury Pacific Marine Jetty, About: https://tilburypacific.ca/about-tilbury-pacific/ - 'Tilbury Jetty Limited Partnership is the proponent of the Tilbury Pacific Marine Jetty Project, an affiliate of FortisBC Holdings Inc.'</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -13470,34 +14399,34 @@
       </c>
       <c r="AE15" s="4" t="inlineStr">
         <is>
+          <t>Tilbury Pacific Marine Jetty, About: https://tilburypacific.ca/about-tilbury-pacific/</t>
+        </is>
+      </c>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>Derived: export project</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us from end_use</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
+        <is>
           <t>Compiled by us</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
-        <is>
-          <t>Derived: export project</t>
-        </is>
-      </c>
-      <c r="AG15" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr">
-        <is>
-          <t>Assigned by us from end_use</t>
-        </is>
-      </c>
-      <c r="AJ15" s="4" t="inlineStr">
-        <is>
-          <t>Compiled by us</t>
-        </is>
-      </c>
       <c r="AK15" s="4" t="inlineStr">
         <is>
           <t>Derived from power_source in this register</t>
@@ -13606,6 +14535,11 @@
       <c r="BF15" t="inlineStr">
         <is>
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -13642,169 +14576,169 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
+          <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html | Canada Investment Summit Prospectus, p. 8: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ - Marinvest Energy Canada, subsidiary of Marinvest Energy AS (Norway)</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ - Marinvest Energy Canada, subsidiary of Marinvest Energy AS (Norway)</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
           <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ - Marinvest Energy Canada, subsidiary of Marinvest Energy AS (Norway)</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ - Marinvest Energy Canada, subsidiary of Marinvest Energy AS (Norway)</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ - not referred to Major Projects Office, no IAAC project description received</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Date we last verified against the sources listed</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>The Narwhal, Baie-Comeau LNG explained: https://thenarwhal.ca/lng-export-project-baie-comeau-quebec/ - not referred to Major Projects Office, no IAAC project description received</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>Date we last verified against the sources listed</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>Derived: classified as an export project</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>Derived: export projects supply no LNG to the domestic market</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>Proponent statements - see sources column</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
         <is>
           <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>Derived: classified as an export project</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>Derived: export projects supply no LNG to the domestic market</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>SeaRates port-to-port distance calculator: https://www.searates.com/distance-time/. Atlantic distances estimated by great circle calculation between port coordinates, scaled by a routing factor of 1.125. That factor was calibrated against a single known sailing distance: SeaRates gives Saint John, New Brunswick to Rotterdam as 5,648 km (3,050 nm) against a great circle of 2,712 nm. Method validated on the Pacific route, where the great circle Kitimat to Tokyo of 3,765 nm closely matches the 3,800 nm figure published by the Oxford Institute for Energy Studies. The routing factor is NOT applied to the Pacific route, where the cited industry figure is used instead, because the factor was calibrated on an Atlantic crossing that must exit the Bay of Fundy and round Nova Scotia.</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 8: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf | Québec Nouvelles: https://www.quebecnouvelles.com/un-troisieme-trace-etudie-pour-livrer-du-gnl-a-baie-comeau-1441870.html | Kino Aski Inc. news release, 17 Aug 2026: https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html | The Energy Mix, 16 Sep 2026: https://www.theenergymix.com/kino-aski-lng-signs-tentative-deal-with-ukraine-state-fossil-as-opposition-rises-complications-abound/</t>
+        </is>
+      </c>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>Derived: export project</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
+          <t>National Observer: https://www.nationalobserver.com/2026/02/20/news/marinvest-quebec-lng-project-ottawa</t>
+        </is>
+      </c>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us from end_use</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
         <is>
           <t>Compiled by us</t>
         </is>
       </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>Proponent statements - see sources column</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
+      <c r="AK16" s="4" t="inlineStr">
+        <is>
+          <t>Assigned gas_turbine, August 2026 electrification revision; previous classification retained in liquefaction_drive_note</t>
+        </is>
+      </c>
+      <c r="AL16" s="4" t="inlineStr">
+        <is>
+          <t>Kino Aski LNG website: https://kinoaskilng.ca/</t>
+        </is>
+      </c>
+      <c r="AM16" s="4" t="inlineStr">
         <is>
           <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
         </is>
       </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>SeaRates port-to-port distance calculator: https://www.searates.com/distance-time/. Atlantic distances estimated by great circle calculation between port coordinates, scaled by a routing factor of 1.125. That factor was calibrated against a single known sailing distance: SeaRates gives Saint John, New Brunswick to Rotterdam as 5,648 km (3,050 nm) against a great circle of 2,712 nm. Method validated on the Pacific route, where the great circle Kitimat to Tokyo of 3,765 nm closely matches the 3,800 nm figure published by the Oxford Institute for Energy Studies. The routing factor is NOT applied to the Pacific route, where the cited industry figure is used instead, because the factor was calibrated on an Atlantic crossing that must exit the Bay of Fundy and round Nova Scotia.</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AB16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr">
-        <is>
-          <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
-        </is>
-      </c>
-      <c r="AF16" s="4" t="inlineStr">
-        <is>
-          <t>Derived: export project</t>
-        </is>
-      </c>
-      <c r="AG16" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AH16" s="4" t="inlineStr">
-        <is>
-          <t>National Observer: https://www.nationalobserver.com/2026/02/20/news/marinvest-quebec-lng-project-ottawa</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr">
-        <is>
-          <t>Assigned by us from end_use</t>
-        </is>
-      </c>
-      <c r="AJ16" s="4" t="inlineStr">
-        <is>
-          <t>Compiled by us</t>
-        </is>
-      </c>
-      <c r="AK16" s="4" t="inlineStr">
-        <is>
-          <t>Assigned gas_turbine, August 2026 electrification revision; previous classification retained in liquefaction_drive_note</t>
-        </is>
-      </c>
-      <c r="AL16" s="4" t="inlineStr">
-        <is>
-          <t>National Observer: https://www.nationalobserver.com/2026/02/20/news/marinvest-quebec-lng-project-ottawa</t>
-        </is>
-      </c>
-      <c r="AM16" s="4" t="inlineStr">
-        <is>
-          <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
-        </is>
-      </c>
       <c r="AN16" s="4" t="inlineStr">
         <is>
           <t>Not available</t>
@@ -13812,7 +14746,7 @@
       </c>
       <c r="AO16" s="4" t="inlineStr">
         <is>
-          <t>Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html</t>
+          <t>Kino Aski LNG website: https://kinoaskilng.ca/</t>
         </is>
       </c>
       <c r="AP16" s="4" t="inlineStr">
@@ -13882,12 +14816,12 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>not available. Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html states no feedgas route or supply basin. No regulatory process has begun.</t>
+          <t>Kino Aski LNG website: https://kinoaskilng.ca/ - '~1,000 KM' of 'new pipeline infrastructure extending Canadian gas networks to Baie-Comeau' | gasworld: https://www.gasworld.com/story/kino-aski-lng-targets-north-america-europe-energy-corridor/2257622.article/ - 'roughly 1,000km of new and existing pipeline infrastructure to transport natural gas from Western Canada to Quebec' | Canada Investment Summit Prospectus (Invest in Canada, Sep 2026), p. 8: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf - 'connect Western Canadian natural gas supplies to the Port of Baie-Comeau'</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>not available. Kino Aski Inc. news release, 17 August 2026, https://www.newswire.ca/news-releases/first-nations-lead-kino-aski-lng-a-major-canadian-energy-project-800865754.html states no feedgas route or supply basin. No regulatory process has begun.</t>
+          <t>Kino Aski LNG website: https://kinoaskilng.ca/ - '~1,000 KM' of 'new pipeline infrastructure extending Canadian gas networks to Baie-Comeau' | gasworld: https://www.gasworld.com/story/kino-aski-lng-targets-north-america-europe-energy-corridor/2257622.article/ - 'roughly 1,000km of new and existing pipeline infrastructure to transport natural gas from Western Canada to Quebec' | Canada Investment Summit Prospectus (Invest in Canada, Sep 2026), p. 8: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf - 'connect Western Canadian natural gas supplies to the Port of Baie-Comeau' | Québec Nouvelles, relaying Radio-Canada (Sep 2026): https://www.quebecnouvelles.com/un-troisieme-trace-etudie-pour-livrer-du-gnl-a-baie-comeau-1441870.html - third route</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -13898,6 +14832,11 @@
       <c r="BF16" t="inlineStr">
         <is>
           <t>not available - Kino Aski LNG has no GEM entry; the register carries no gem_wiki_url for it</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -14192,6 +15131,11 @@
           <t>not available - no gem_wiki_url in the register; the project is tracked through NRCan, IAAC and the BC EAO instead</t>
         </is>
       </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14226,7 +15170,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Fermeuse_Energy_FLNG_Terminal</t>
+          <t>The Narwhal, 19 Mar 2026: https://thenarwhal.ca/lng-newfoundland-lessons-kitimat-bc/ | GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Fermeuse_Energy_FLNG_Terminal</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -14281,12 +15225,12 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Derived from proponent-stated 9.7 Tcf Jeanne d'Arc resource over 40 years, net of liquefaction fuel at the model's own liquefaction and combustion factors; not a published nameplate. Fermeuse Energy news release, 2 September 2025.</t>
+          <t>The Narwhal, 19 Mar 2026: https://thenarwhal.ca/lng-newfoundland-lessons-kitimat-bc/ - Crown LNG chief executive Swapan Kataria: the plant would 'process and export up to 10 million tonnes of LNG per year'. A developer statement to journalists, not a filed or published nameplate. Adopted 27 Sep 2026 in place of the 4.5 mtpa derivation. Same figure on GEM wiki: https://www.gem.wiki/Fermeuse_Energy_FLNG_Terminal</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>Compiled by us; derivation recorded step by step in capacity_basis</t>
+          <t>The Narwhal, 19 Mar 2026: https://thenarwhal.ca/lng-newfoundland-lessons-kitimat-bc/</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr">
@@ -14401,7 +15345,7 @@
       </c>
       <c r="AP18" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Derived, not stated. The developer's 9.7 Tcf (275 bcm) Jeanne d'Arc resource (Fermeuse Energy news release, 2 Sep 2025) divided by annual feedgas at the developer's 10 mtpa (The Narwhal, 19 Mar 2026: https://thenarwhal.ca/lng-newfoundland-lessons-kitimat-bc/): 10 mtpa x 1.38 bcm per mtpa x 1.1055 t feedgas per t LNG (fuel netted at the model's 0.29 / 2.75 factors, as in the superseded capacity derivation) = 15.26 bcm a year; 275 / 15.26 = 18.0 years at full output. Holding life to the resource keeps lifetime gas within the developer's own claim: 10 mtpa for 40 years would need about 610 bcm (21.5 Tcf). Model note: for pre-FID assets the FID delay sits inside this window, which shortens operating years (code decision pending).</t>
         </is>
       </c>
       <c r="AQ18" s="4" t="inlineStr">
@@ -14482,6 +15426,11 @@
       <c r="BF18" t="inlineStr">
         <is>
           <t>GEM wiki, read 2026-08-28: https://www.gem.wiki/Fermeuse_Energy_FLNG_Terminal - status field quoted verbatim. gem_status_date is the page's last-modified date.</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -14578,7 +15527,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
@@ -14774,6 +15723,11 @@
       <c r="BF19" t="inlineStr">
         <is>
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -15068,6 +16022,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15360,6 +16319,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15652,6 +16616,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15944,6 +16913,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16236,6 +17210,11 @@
           <t>GEM wiki, read 2026-08-29: https://www.gem.wiki/Discovery_LNG_Terminal - status field quoted verbatim. gem_status_date is the page's last-modified date.</t>
         </is>
       </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16528,6 +17507,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16552,17 +17536,17 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Assigned by us from status, regulatory stage and FID - see tier_reason</t>
+          <t>Assigned by us - see tier_reason</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Derived: advanced_proposed and early_proposed group as proposed</t>
+          <t>Assigned: watch rows are excluded from all totals</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Kitimat_LNG_Terminal</t>
+          <t>yáqʷa Development Corporation, 17 Nov 2025: https://www.yaqwadevcorp.com/2025/11/18/yaq%CA%B7a-acquisition/ | BC EAO project record (EPIC): https://projects.eao.gov.bc.ca/api/public/search?dataset=Project&amp;keywords=Kitimat&amp;pageNum=0&amp;pageSize=100 | GEM wiki: https://www.gem.wiki/Kitimat_LNG_Terminal</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -16577,17 +17561,17 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ Operator</t>
+          <t>BC EAO project record (EPIC): https://projects.eao.gov.bc.ca/api/public/search?dataset=Project&amp;keywords=Kitimat&amp;pageNum=0&amp;pageSize=100</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ Parent</t>
+          <t>yáqʷa Development Corporation, 17 Nov 2025: https://www.yaqwadevcorp.com/2025/11/18/yaq%CA%B7a-acquisition/</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ Status</t>
+          <t>BC EAO project record (EPIC): https://projects.eao.gov.bc.ca/api/public/search?dataset=Project&amp;keywords=Kitimat&amp;pageNum=0&amp;pageSize=100 - 'Post Decision - Care &amp; Maintenance'. The Chevron-Woodside project was cancelled (GEM GGIT, Sep 2025: https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/); the certified site and permits survive under new ownership.</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -16612,7 +17596,7 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>yáqʷa Development Corporation, 17 Nov 2025: https://www.yaqwadevcorp.com/2025/11/18/yaq%CA%B7a-acquisition/</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr">
@@ -16702,7 +17686,7 @@
       </c>
       <c r="AI26" s="4" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Assigned by us: former export proposal. Needed because the row carries a capacity; watch rows are excluded from all totals.</t>
         </is>
       </c>
       <c r="AJ26" s="4" t="inlineStr">
@@ -16818,6 +17802,11 @@
       <c r="BF26" t="inlineStr">
         <is>
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -17112,6 +18101,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17404,6 +18398,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17696,6 +18695,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17988,6 +18992,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18280,6 +19289,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -18572,6 +19586,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18864,6 +19883,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19156,6 +20180,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19448,6 +20477,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19740,6 +20774,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20032,6 +21071,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20324,6 +21368,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20616,6 +21665,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20908,6 +21962,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21200,6 +22259,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21492,6 +22556,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21526,7 +22595,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Placentia_Bay_FLNG_Terminal</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | GEM wiki: https://www.gem.wiki/Placentia_Bay_FLNG_Terminal | NL environmental assessment projects list: https://www.gov.nl.ca/ecc/env-assessment/projects-list/</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -21541,7 +22610,7 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Newfoundland and Labrador environmental assessment projects list: https://www.gov.nl.ca/ecc/env-assessment/projects-list/ - registration 2177</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -21782,6 +22851,11 @@
       <c r="BF43" t="inlineStr">
         <is>
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -22076,6 +23150,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -22368,6 +23447,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -22660,6 +23744,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -22952,6 +24041,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -23244,6 +24338,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -23536,6 +24635,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG49" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -23828,6 +24932,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -24120,6 +25229,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG51" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -24412,6 +25526,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG52" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24704,6 +25823,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -24996,6 +26120,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -25288,6 +26417,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25580,6 +26714,11 @@
           <t>not available - outside the headline export scope; the GEM page was not read for this row</t>
         </is>
       </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25614,262 +26753,1455 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
+          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html | LNG Industry, 14 Sep 2026: https://www.lngindustry.com/floating-lng/14092026/kanata-clean-power-and-hanwha-ocean-to-launch-pre-feed-for-proposed-floating-lng-project/</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Energy Intelligence, 18 June 2026, https://www.energyintel.com/0000019e-d707-d1c7-a9bf-ff5fb8d50000</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html | Energy Intelligence, 18 June 2026, https://www.energyintel.com/0000019e-d707-d1c7-a9bf-ff5fb8d50000</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
           <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>LNG Industry, 14 Sep 2026: https://www.lngindustry.com/floating-lng/14092026/kanata-clean-power-and-hanwha-ocean-to-launch-pre-feed-for-proposed-floating-lng-project/</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>Date we last verified against the sources listed</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>Derived: classified as an export project</t>
+        </is>
+      </c>
+      <c r="U57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>Derived: export projects supply no LNG to the domestic market</t>
+        </is>
+      </c>
+      <c r="W57" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="X57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Y57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Z57" s="4" t="inlineStr">
+        <is>
+          <t>CAPP, The Case for Canadian LNG (Apr 2026), citing Oxford Institute for Energy Studies: https://www.capp.ca/wp-content/uploads/2026/05/The-Case-for-Canadian-LNG-April-17-2026.pdf - west coast Canada to Tokyo approximately 3,800 nautical miles. Applied here as the west-coast-Canada basis, not a port-specific sailing distance: no published port-to-port distance was located for this terminal. Same basis as the other British Columbia export assets in the register.</t>
+        </is>
+      </c>
+      <c r="AA57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AB57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AD57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AE57" s="4" t="inlineStr">
         <is>
           <t>Energy Intelligence, 18 June 2026, https://www.energyintel.com/0000019e-d707-d1c7-a9bf-ff5fb8d50000</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html | Energy Intelligence, 18 June 2026, https://www.energyintel.com/0000019e-d707-d1c7-a9bf-ff5fb8d50000</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="AF57" s="4" t="inlineStr">
         <is>
           <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
+      <c r="AG57" s="4" t="inlineStr">
         <is>
           <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="AH57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI57" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us from end_use</t>
+        </is>
+      </c>
+      <c r="AJ57" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AK57" s="4" t="inlineStr">
+        <is>
+          <t>Assigned gas_turbine, August 2026 electrification revision; previous classification retained in liquefaction_drive_note</t>
+        </is>
+      </c>
+      <c r="AL57" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AM57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AN57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AO57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AP57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AQ57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AS57" s="4" t="inlineStr">
+        <is>
+          <t>CER Export Licence Applications schedule</t>
+        </is>
+      </c>
+      <c r="AT57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AU57" s="4" t="inlineStr">
+        <is>
+          <t>Not available - project does not appear in GEM GGIT LNG Terminals Sep 2025</t>
+        </is>
+      </c>
+      <c r="AV57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AW57" s="4" t="inlineStr">
+        <is>
+          <t>NRCan Canadian LNG projects: not present as of August 2026</t>
+        </is>
+      </c>
+      <c r="AX57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AY57" s="4" t="inlineStr">
+        <is>
+          <t>CER Export Licence Applications schedule</t>
+        </is>
+      </c>
+      <c r="AZ57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BA57" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BB57" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us from the sources named in this row</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>not available - Kanata LNG was added from proponent sources in June 2026 and is not in GEM</t>
+        </is>
+      </c>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>not available - Kanata LNG was added from proponent sources in June 2026 and is not in GEM</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>northern_prince_lng</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us - see tier_reason</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Assigned: watch rows are excluded from all totals</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about | NeeStaNan: https://neestanan.ca/neestanan-and-lng-exports/ | BOE Report, 5 Mar 2024: https://boereport.com/2024/03/05/neestanan-signs-mou-with-northern-prince-lng/ | CER REGDOCS filing titles (documents not opened): https://apps.cer-rec.gc.ca/REGDOCS/Item/View/4459935</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>NeeStaNan: https://neestanan.ca/neestanan-and-lng-exports/ - 'near Summit Lake, British Columbia'</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>Date we last verified against the sources listed</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="O57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="P57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="R57" s="4" t="inlineStr">
-        <is>
-          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
-        </is>
-      </c>
-      <c r="S57" s="4" t="inlineStr">
-        <is>
-          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
-        </is>
-      </c>
-      <c r="T57" s="4" t="inlineStr">
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>CER REGDOCS: https://apps.cer-rec.gc.ca/REGDOCS/Item/View/4459935 - filing titles 'Application for Short-Term Natural Gas Export Orders' (C20575, C29880) and 'Order GO-116-2022'; documents not opened (REGDOCS unreachable)</t>
+        </is>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about - 'executed HOA's for 6MMTPA for our larger project'; NeeStaNan: https://neestanan.ca/neestanan-and-lng-exports/ - '6 million tonne per annum (mtpa) LNG manufacturing facility'</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="T58" s="4" t="inlineStr">
         <is>
           <t>Derived: classified as an export project</t>
         </is>
       </c>
-      <c r="U57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="V57" s="4" t="inlineStr">
+      <c r="U58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="inlineStr">
         <is>
           <t>Derived: export projects supply no LNG to the domestic market</t>
         </is>
       </c>
-      <c r="W57" s="4" t="inlineStr">
+      <c r="W58" s="4" t="inlineStr">
         <is>
           <t>Compiled by us</t>
         </is>
       </c>
-      <c r="X57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Y57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Z57" s="4" t="inlineStr">
-        <is>
-          <t>CAPP, The Case for Canadian LNG (Apr 2026), citing Oxford Institute for Energy Studies: https://www.capp.ca/wp-content/uploads/2026/05/The-Case-for-Canadian-LNG-April-17-2026.pdf - west coast Canada to Tokyo approximately 3,800 nautical miles. Applied here as the west-coast-Canada basis, not a port-specific sailing distance: no published port-to-port distance was located for this terminal. Same basis as the other British Columbia export assets in the register.</t>
-        </is>
-      </c>
-      <c r="AA57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AB57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AC57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AD57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AE57" s="4" t="inlineStr">
-        <is>
-          <t>Energy Intelligence, 18 June 2026, https://www.energyintel.com/0000019e-d707-d1c7-a9bf-ff5fb8d50000</t>
-        </is>
-      </c>
-      <c r="AF57" s="4" t="inlineStr">
-        <is>
-          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
-        </is>
-      </c>
-      <c r="AG57" s="4" t="inlineStr">
-        <is>
-          <t>Hanwha Ocean news release, 16 June 2026, https://www.newswire.ca/news-releases/hanwha-ocean-signs-strategic-memorandum-of-understanding-with-kanata-clean-power-for-proposed-floating-lng-project-in-canada-867061587.html</t>
-        </is>
-      </c>
-      <c r="AH57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AI57" s="4" t="inlineStr">
+      <c r="X58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="Y58" s="4" t="inlineStr">
+        <is>
+          <t>BOE Report, 5 Mar 2024: https://boereport.com/2024/03/05/neestanan-signs-mou-with-northern-prince-lng/</t>
+        </is>
+      </c>
+      <c r="Z58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AA58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AB58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AD58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AE58" s="4" t="inlineStr">
+        <is>
+          <t>BOE Report, 5 Mar 2024: https://boereport.com/2024/03/05/neestanan-signs-mou-with-northern-prince-lng/ | BOE Report, 2 Jul 2025: https://boereport.com/2025/07/02/neestanan-and-fox-lake-cree-nation-secure-federal-authorization-to-export-lng/ | Website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="AF58" s="4" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG website: https://www.northernprincelng.com/about</t>
+        </is>
+      </c>
+      <c r="AG58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AH58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI58" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us: stated export project. Watch rows are excluded from all totals.</t>
+        </is>
+      </c>
+      <c r="AJ58" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AK58" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="AL58" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AM58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AN58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AO58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AP58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AQ58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AR58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AS58" s="4" t="inlineStr">
+        <is>
+          <t>CER REGDOCS: https://apps.cer-rec.gc.ca/REGDOCS/Item/View/4459935</t>
+        </is>
+      </c>
+      <c r="AT58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AU58" s="4" t="inlineStr">
+        <is>
+          <t>Not available - does not appear in GEM GGIT LNG Terminals Sep 2025</t>
+        </is>
+      </c>
+      <c r="AV58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AW58" s="4" t="inlineStr">
+        <is>
+          <t>NRCan Canadian LNG projects: not present (page modified 7 Jan 2025)</t>
+        </is>
+      </c>
+      <c r="AX58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AY58" s="4" t="inlineStr">
+        <is>
+          <t>CER REGDOCS: https://apps.cer-rec.gc.ca/REGDOCS/Item/View/4459935</t>
+        </is>
+      </c>
+      <c r="AZ58" s="4" t="inlineStr">
+        <is>
+          <t>CER REGDOCS</t>
+        </is>
+      </c>
+      <c r="BA58" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BB58" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us from the sources named in this row</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>not available - watch row, excluded from all totals; no feedgas route stated</t>
+        </is>
+      </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BE58" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BF58" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BG58" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>hudson_bay_churchill_lng</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Port of Churchill Plus LNG (floating LNG concept)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us - see tier_reason</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Assigned: watch rows are excluded from all totals</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Major Projects Office, Port of Churchill Plus: https://www.canada.ca/en/privy-council/major-projects-office/projects/other/referred/churchill-plus.html | Canada Investment Summit Prospectus, p. 40: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf | CBC via Yahoo, 15 Sep 2026: https://ca.news.yahoo.com/port-churchill-railway-improvements-cost-100000703.html | The Deep Dive, 15 Sep 2026: https://thedeepdive.ca/manitoba-pitches-pst-exemption-to-drive-port-of-churchill-investment/ | Global News, 17 Apr 2026: https://globalnews.ca/news/11806964/federal-government-puts-timeline-in-place-for-port-of-churchill-project-kinew/</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Major Projects Office: https://www.canada.ca/en/privy-council/major-projects-office/projects/other/referred/churchill-plus.html</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CBC via Yahoo, 15 Sep 2026: https://ca.news.yahoo.com/port-churchill-railway-improvements-cost-100000703.html</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>CBC via Yahoo, 15 Sep 2026: https://ca.news.yahoo.com/port-churchill-railway-improvements-cost-100000703.html; The Deep Dive: https://thedeepdive.ca/manitoba-pitches-pst-exemption-to-drive-port-of-churchill-investment/</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 40: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>Date we last verified against the sources listed</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>Not available - no source states a capacity; blank rather than estimated</t>
+        </is>
+      </c>
+      <c r="S59" s="4" t="inlineStr">
+        <is>
+          <t>Not available - no source states a capacity</t>
+        </is>
+      </c>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>Derived: classified as an export concept</t>
+        </is>
+      </c>
+      <c r="U59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="W59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="X59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Y59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Z59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AA59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AB59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AD59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AE59" s="4" t="inlineStr">
+        <is>
+          <t>Global News, 17 Apr 2026: https://globalnews.ca/news/11806964/federal-government-puts-timeline-in-place-for-port-of-churchill-project-kinew/</t>
+        </is>
+      </c>
+      <c r="AF59" s="4" t="inlineStr">
+        <is>
+          <t>CBC via Yahoo, 15 Sep 2026: https://ca.news.yahoo.com/port-churchill-railway-improvements-cost-100000703.html</t>
+        </is>
+      </c>
+      <c r="AG59" s="4" t="inlineStr">
+        <is>
+          <t>CBC via Yahoo, 15 Sep 2026: https://ca.news.yahoo.com/port-churchill-railway-improvements-cost-100000703.html</t>
+        </is>
+      </c>
+      <c r="AH59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI59" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us: export concept. Watch rows are excluded from all totals.</t>
+        </is>
+      </c>
+      <c r="AJ59" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AK59" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="AL59" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AM59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AN59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AO59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AP59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AQ59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AR59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AS59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AT59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AU59" s="4" t="inlineStr">
+        <is>
+          <t>Not available - does not appear in GEM GGIT LNG Terminals Sep 2025</t>
+        </is>
+      </c>
+      <c r="AV59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AW59" s="4" t="inlineStr">
+        <is>
+          <t>NRCan Canadian LNG projects: not present (page modified 7 Jan 2025)</t>
+        </is>
+      </c>
+      <c r="AX59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AY59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AZ59" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BA59" s="4" t="inlineStr">
+        <is>
+          <t>Major Projects Office</t>
+        </is>
+      </c>
+      <c r="BB59" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us from the sources named in this row</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>not available - watch row, excluded from all totals; no feedgas route stated</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BE59" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BF59" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BG59" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>neestanan_port_nelson_lng</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NeeStaNan Port Nelson LNG export (feasibility)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us - see tier_reason</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Assigned: watch rows are excluded from all totals</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120 | BOE Report, 2 Jul 2025: https://boereport.com/2025/07/02/neestanan-and-fox-lake-cree-nation-secure-federal-authorization-to-export-lng/</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>BOE Report, 2 Jul 2025: https://boereport.com/2025/07/02/neestanan-and-fox-lake-cree-nation-secure-federal-authorization-to-export-lng/</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120 - feasibility study phase</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>Date we last verified against the sources listed</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120; BOE Report, 2 Jul 2025: https://boereport.com/2025/07/02/neestanan-and-fox-lake-cree-nation-secure-federal-authorization-to-export-lng/</t>
+        </is>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>Not available - no capacity stated; blank rather than estimated</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>Not available - no capacity stated</t>
+        </is>
+      </c>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>Derived: classified as an export concept</t>
+        </is>
+      </c>
+      <c r="U60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="V60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="W60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="X60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Y60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Z60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AA60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AB60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AD60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AE60" s="4" t="inlineStr">
+        <is>
+          <t>BOE Report, 2 Jul 2025: https://boereport.com/2025/07/02/neestanan-and-fox-lake-cree-nation-secure-federal-authorization-to-export-lng/</t>
+        </is>
+      </c>
+      <c r="AF60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120</t>
+        </is>
+      </c>
+      <c r="AG60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AH60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI60" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us: export concept. Watch rows are excluded from all totals.</t>
+        </is>
+      </c>
+      <c r="AJ60" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AK60" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="AL60" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="AM60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AN60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AO60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AP60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AQ60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AR60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AS60" s="4" t="inlineStr">
+        <is>
+          <t>CBC: https://www.cbc.ca/1.7582120</t>
+        </is>
+      </c>
+      <c r="AT60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AU60" s="4" t="inlineStr">
+        <is>
+          <t>Not available - does not appear in GEM GGIT LNG Terminals Sep 2025</t>
+        </is>
+      </c>
+      <c r="AV60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AW60" s="4" t="inlineStr">
+        <is>
+          <t>NRCan Canadian LNG projects: not present (page modified 7 Jan 2025)</t>
+        </is>
+      </c>
+      <c r="AX60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AY60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AZ60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BA60" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BB60" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us from the sources named in this row</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>not available - watch row, excluded from all totals; no feedgas route stated</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BE60" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BF60" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>project_northern_lights_lng</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Project Northern Lights (Cool LNG)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Assigned by us - see tier_reason</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Assigned: proposed</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus (Sep 2026), p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf - 'Shovel-ready'</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Date we last verified against the sources listed</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>Not available - no FID stated</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>Not available - capacity not published; blank rather than estimated</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="U61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="V61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="W61" s="4" t="inlineStr">
+        <is>
+          <t>Compiled by us</t>
+        </is>
+      </c>
+      <c r="X61" s="4" t="inlineStr">
+        <is>
+          <t>Derived: domestic facility</t>
+        </is>
+      </c>
+      <c r="Y61" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="Z61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AA61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AB61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AD61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AE61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AF61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="AG61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AH61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AI61" s="4" t="inlineStr">
         <is>
           <t>Assigned by us from end_use</t>
         </is>
       </c>
-      <c r="AJ57" s="4" t="inlineStr">
+      <c r="AJ61" s="4" t="inlineStr">
         <is>
           <t>Compiled by us</t>
         </is>
       </c>
-      <c r="AK57" s="4" t="inlineStr">
-        <is>
-          <t>Assigned gas_turbine, August 2026 electrification revision; previous classification retained in liquefaction_drive_note</t>
-        </is>
-      </c>
-      <c r="AL57" s="4" t="inlineStr">
-        <is>
-          <t>Compiled by us</t>
-        </is>
-      </c>
-      <c r="AM57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AN57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AO57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AP57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AQ57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AR57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AS57" s="4" t="inlineStr">
-        <is>
-          <t>CER Export Licence Applications schedule</t>
-        </is>
-      </c>
-      <c r="AT57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AU57" s="4" t="inlineStr">
-        <is>
-          <t>Not available - project does not appear in GEM GGIT LNG Terminals Sep 2025</t>
-        </is>
-      </c>
-      <c r="AV57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AW57" s="4" t="inlineStr">
-        <is>
-          <t>NRCan Canadian LNG projects: not present as of August 2026</t>
-        </is>
-      </c>
-      <c r="AX57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="AY57" s="4" t="inlineStr">
-        <is>
-          <t>CER Export Licence Applications schedule</t>
-        </is>
-      </c>
-      <c r="AZ57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="BA57" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="BB57" s="4" t="inlineStr">
+      <c r="AK61" s="4" t="inlineStr">
+        <is>
+          <t>Not published for small plants</t>
+        </is>
+      </c>
+      <c r="AL61" s="4" t="inlineStr">
+        <is>
+          <t>Canada Investment Summit Prospectus, p. 7: https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf</t>
+        </is>
+      </c>
+      <c r="AM61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AN61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AO61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AP61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AQ61" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AR61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AS61" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AT61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AU61" s="4" t="inlineStr">
+        <is>
+          <t>Not available - does not appear in GEM GGIT LNG Terminals Sep 2025</t>
+        </is>
+      </c>
+      <c r="AV61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AW61" s="4" t="inlineStr">
+        <is>
+          <t>NRCan Canadian LNG projects: not present (page modified 7 Jan 2025)</t>
+        </is>
+      </c>
+      <c r="AX61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AY61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AZ61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BA61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BB61" s="4" t="inlineStr">
         <is>
           <t>Compiled by us from the sources named in this row</t>
         </is>
       </c>
-      <c r="BC57" t="inlineStr">
-        <is>
-          <t>not available</t>
-        </is>
-      </c>
-      <c r="BD57" t="inlineStr">
-        <is>
-          <t>not available</t>
-        </is>
-      </c>
-      <c r="BE57" t="inlineStr">
-        <is>
-          <t>not available - Kanata LNG was added from proponent sources in June 2026 and is not in GEM</t>
-        </is>
-      </c>
-      <c r="BF57" t="inlineStr">
-        <is>
-          <t>not available - Kanata LNG was added from proponent sources in June 2026 and is not in GEM</t>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>not available - no capacity, so no lifecycle is computed</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="BE61" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BF61" t="inlineStr">
+        <is>
+          <t>not available - no GEM entry</t>
+        </is>
+      </c>
+      <c r="BG61" t="inlineStr">
+        <is>
+          <t>Not applicable. Blank = False: the asset has an FID, or its first_export_year is not a developer date that already allows for the build after an FID, so fid_delay_mid applies as before.</t>
         </is>
       </c>
     </row>
@@ -26024,17 +28356,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17.3</v>
+        <v>17.75</v>
       </c>
       <c r="J2" t="n">
-        <v>23.87</v>
+        <v>24.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.41</v>
+        <v>-3.04</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>SHORTFALL of 2.41 bcm/y</t>
+          <t>SHORTFALL of 3.04 bcm/y</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
@@ -26054,7 +28386,7 @@
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT Gas Pipelines (Nov 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/; BC Environmental Assessment Office 2014 assessment report; BC Energy Regulator project page: https://www.bc-er.ca/what-we-regulate/major-projects/coastal-gaslink/</t>
+          <t>GEM GGIT Gas Pipelines (Nov 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/; BC Environmental Assessment Office 2014 assessment report; BC Energy Regulator project page: https://www.bc-er.ca/what-we-regulate/major-projects/coastal-gaslink/ | Cedar at 3.75 mtpa from 27 Sep 2026 (BC EAO amendment): https://projects.eao.gov.bc.ca/api/public/document/68caf0067a03b4002205daf9/download/Cedar%20LNG%20Accommodation%20+%20Capacity%20Amendment%20Application.pdf</t>
         </is>
       </c>
     </row>
@@ -26391,7 +28723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -26907,7 +29239,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Nameplate design export capacity. The single most important input to every headline number. Convention: nameplate, with regulator or licenced figures recorded in capacity_basis where they differ.</t>
+          <t>Design export capacity. The single most important input to every headline number. Convention: the latest design figure published by the developer or permitted by a regulator, with other figures recorded in capacity_basis where they differ.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -27187,7 +29519,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Operating life where the proponent states one. Only Summit Lake PG LNG does, at 30 years. There is deliberately no blanket default.</t>
+          <t>Operating life where the developer states one (Summit Lake PG LNG, 30 years) or where it follows from the developer's own statements (Fermeuse, 18 years: stated resource at stated capacity, derivation in the source cell). There is deliberately no blanket default.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -27931,6 +30263,38 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>sourced</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>first_export_year_assumes_fid</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Asset Register</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>True when first_export_year is a developer date that already allows for the build after an FID (for example a delivery start in an offtake agreement). The model then does not add fid_delay_mid to that pre-FID asset. Blank means False.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>assigned</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Judgement from the source of first_export_year, stated in the Asset Sources cell. Added 27 Sep 2026.</t>
         </is>
       </c>
     </row>
@@ -27946,7 +30310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28002,22 +30366,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Derived 4.5 mtpa</t>
+          <t>Developer statement 10 mtpa; life derived 18 years</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Proponent has not published a liquefaction capacity. 4.5 mtpa is derived from the stated 9.7 Tcf Jeanne d'Arc resource over a 40-year life at 1.38 bcm per mtpa, net of liquefaction fuel at the model's own factors (was 5.0 before netting fuel, 3 September 2026). Conditional on the proponent's resource claim; full recovery on a flat profile pushes it up. Higher figures (about 8 from a 25-year life; 9-12 from capital-cost benchmarking; an unsourced 10 mtpa) were not used.</t>
+          <t>Crown LNG's chief executive stated up to 10 mtpa (The Narwhal, 19 Mar 2026: https://thenarwhal.ca/lng-newfoundland-lessons-kitimat-bc/). No filing states capacity or life. The 18-year life is derived from the developer's 9.7 Tcf resource at 10 mtpa, net of liquefaction fuel. Supersedes the 4.5 mtpa derivation of 3 Sep 2026.</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>A filed project description stating liquefaction capacity.</t>
+          <t>A filed project description stating liquefaction capacity and production profile.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>high - derived figure now enters totals; replace when a published capacity exists</t>
+          <t>high - a developer statement, not a filing; the derived life sets the lifetime total</t>
         </is>
       </c>
     </row>
@@ -28066,22 +30430,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RESOLVED - 3.3 nameplate</t>
+          <t>UPDATED - 3.75 permitted</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Settled against the proponent's own FID announcement, which states nameplate 3.3 mtpa. NRCan and CER's 3.0 treated as licenced or rounded.</t>
+          <t>The BC EAO's amended certificate (July 2026) permits 500 mmscfd, 3.75 mtpa, from the same equipment (https://projects.eao.gov.bc.ca/api/public/document/68caf0067a03b4002205daf9/download/Cedar%20LNG%20Accommodation%20+%20Capacity%20Amendment%20Application.pdf; https://www.giignl.org/news/cedar-lng-receives-approval-to-increase-project-capacity). The FID announcement said 3.3; NRCan and the CER give 3.0, the pre-amendment basis. Still subject to IAAC and BC Energy Regulator approval.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>IAAC decision statement amendment and BC Energy Regulator permit</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>low - 0.45 mtpa</t>
         </is>
       </c>
     </row>
@@ -28098,22 +30462,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.5 retained</t>
+          <t>RESOLVED - 2.5 addition retained</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>GEM records Phase 2 as a 2.5 mtpa addition. Local reporting says Phase 2 brings TOTAL site capacity to 2.5, implying an addition of ~1.6. LNG Prime cites ~2.6 for the liquefaction component.</t>
+          <t>The 21 Sep 2026 certificate covers up to 7,700 t/d of new liquefaction (2.8 Mt a year at 365 days: https://surreynowleader.com/2026/09/21/delta-lng-expansion-project-issued-b-c-environmental-assessment-certificate/), consistent with GEM's 2.5 mtpa addition and not with the ~1.6 implied by earlier local reporting.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>FortisBC or BC EAO filing</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>medium - only if Tilbury is counted as export</t>
+          <t>closed</t>
         </is>
       </c>
     </row>
@@ -28322,22 +30686,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2028 used</t>
+          <t>RESOLVED - 2027 used</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>GEM says 2028, Norton Rose and CER say 2027</t>
+          <t>The developer's latest statement targets in service at end-2027 (LNG Journal, 16 Jul 2026: https://lngjournal.com/index.php/latest-news-mainmenu-47/item/116798-woodfibre-lng-on-track-to-complete-construction-by-late-2027). GEM (Sep 2025) said 2028; Norton Rose and the CER 2027. The latest developer year is used (27 Sep 2026).</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Proponent schedule</t>
+          <t>Closed; revisit if first cargo slips into 2028</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>medium - shifts ramp by one year</t>
+          <t>closed</t>
         </is>
       </c>
     </row>
@@ -28578,22 +30942,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>RESOLVED - Tilbury Jetty Limited Partnership</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>NRCan names the project but not the proponent. WesPac Midstream-Vancouver holds GL-310 for Delta BC, match inferred not confirmed</t>
+          <t>The project site (https://tilburypacific.ca/about-tilbury-pacific/) names Tilbury Jetty Limited Partnership, a FortisBC Holdings affiliate, as proponent. Whether WesPac's GL-310 relates to this project is still unconfirmed.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>CER REGDOCS or FortisBC filings</t>
+          <t>CER REGDOCS for the GL-310 link</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>low - no capacity attached</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -28738,22 +31102,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>not available</t>
+          <t>RESOLVED at basin level - Western Canada (developer-stated)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The proponent has stated no feedgas route or supply basin and no regulatory process has begun. The two candidates - Western Canadian gas via the TC Energy Mainline, and United States Appalachian gas - differ both in pipeline transport distance and in whether upstream and pipeline emissions are Canada territorial.</t>
+          <t>The developer names Western Canadian gas carried over existing networks plus about 1,000 km of new pipeline (https://kinoaskilng.ca/; https://www.gasworld.com/story/kino-aski-lng-targets-north-america-europe-energy-corridor/2257622.article/; federal prospectus p. 8, https://cabinradio.ca/wp-content/uploads/2026/09/CanadaInvestmentSummit.pdf). No source states US supply.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>A filed project description or regulatory application stating the feedgas source and route.</t>
+          <t>A filed route naming the producing area and pipeline corridor.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>high - decides 15 mtpa of territorial attribution; run as an explicit sensitivity in the meantime</t>
+          <t>medium - the Canadian territorial attribution is settled; the pipeline distance is not</t>
         </is>
       </c>
     </row>
@@ -28775,7 +31139,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No published route distance exists for Western Canadian gas to the Quebec north shore, because no such route is defined. The CER pipeline profile for the TransCanada Canadian Mainline publishes only a total regulated system length of 14,123 km covering all segments including deactivated and abandoned ones (https://apps.cer-rec.gc.ca/PPS/en/pipeline-profiles/transcanada-canadian-mainline-tc), which is not a route distance, and Baie-Comeau is not on the Mainline in any case.</t>
+          <t>No published route distance exists for Western Canadian gas to the Quebec north shore, because no such route is defined. The CER pipeline profile for the TransCanada Canadian Mainline publishes only a total regulated system length of 14,123 km covering all segments including deactivated and abandoned ones (https://apps.cer-rec.gc.ca/PPS/en/pipeline-profiles/transcanada-canadian-mainline-tc), which is not a route distance, and Baie-Comeau is not on the Mainline in any case. Update Sep 2026: the developer describes about 1,000 km of new pipeline added to existing Canadian networks, and three corridors are under study (https://kinoaskilng.ca/; https://www.quebecnouvelles.com/un-troisieme-trace-etudie-pour-livrer-du-gnl-a-baie-comeau-1441870.html), so a route distance still cannot be computed.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -28882,6 +31246,166 @@
       <c r="F29" t="inlineStr">
         <is>
           <t>closed - register now matches GEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Northern Prince LNG</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Watch; 6 mtpa developer claim</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No filed project description, named buyer, named site or long-term CER licence. The only CER records are short-term export order filings (titles only). Possible overlap with Summit Lake PG LNG.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>A filed project description, a named HOA buyer, a named site or a long-term licence application</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>medium - as a proposed row 6 mtpa would add about 610 MtCO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>capacity_mtpa / proponent</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Port of Churchill Plus LNG</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No developer and no stated capacity; the LNG element is a government concept.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>A named developer and a stated liquefaction capacity</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>medium - federal 2030 target</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>capacity_mtpa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NeeStaNan Port Nelson</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Feasibility study under a short-term CER authorisation; no capacity stated.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Feasibility study results or a filed project description</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>capacity_mtpa / location</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Project Northern Lights (Cool LNG)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>The federal prospectus gives cost and permitting status but no capacity or site.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Developer statement of capacity and site, or the Alberta permit record</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>low - domestic, outside the headline</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dawson Creek LNG, Elmworth LNG, Hagar LNG, Linde Fort Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Not added</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Candidate domestic plants from the 26 Sep 2026 research sweep. Their sources could not be opened, or did not confirm current operation (Campus Energy's site no longer lists Dawson Creek).</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>An operator page or regulator record confirming operation and capacity</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>low - domestic, outside the headline</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Asset_Register.xlsx
+++ b/Inputs/Canada_LNG_Asset_Register.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Sources" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supporting Infrastructure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Definitions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Gaps" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Asset Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Asset Sources" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Supporting Infrastructure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Field Definitions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Data Gaps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Asset Register'!$A$1:$BB$56</definedName>
@@ -27,7 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -111,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +130,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -972,7 +975,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>It carries 21.46 bcm/y and already serves 24.50 from LNG Canada Phase 1 plus Cedar (3.75 mtpa since the July 2026 certificate amendment), whose 8 km connector draws on it. Phase 2's 14 mtpa, 31 per cent of live export capacity, depends on the proposed second line agreed only in principle in March 2026.</t>
+          <t>It carries 21.46 bcm/y and already serves 24.50 from LNG Canada Phase 1 plus Cedar (3.75 mtpa since the July 2026 certificate amendment), whose 8 km connector draws on it. Phase 2's 14 mtpa depends on the Coastal GasLink expansion, which will proceed following the LNG Canada Phase 2 final investment decision of 29 September 2026.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1027,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -1052,7 +1054,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>No FID yet. Status text refreshed; first LNG 2030 reconfirmed (GEM wiki, 25 Sep 2026: https://www.gem.wiki/LNG_Canada_Terminal).</t>
+          <t>Final investment decision 29 Sep 2026. Status construction, tier and calc_group under_construction, first LNG 2031 (decision date plus the IEA 4 to 5 year lag; Shell expects commercial operations in the early 2030s).</t>
         </is>
       </c>
     </row>
@@ -3325,17 +3327,17 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>advanced_proposed</t>
+          <t>under_construction</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>under_construction</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Referred to the Major Projects Office Sep 2025 and designated national interest. Canada, British Columbia and LNG Canada agreed enhanced investment co-operation on 14 May 2026, targeting a 2026 FID. LNG Canada issued a limited notice to proceed to the JGC-Fluor joint venture in June 2026. Reuters reported on 24 Sep 2026 that an FID could come as early as October, and LNG Canada hopes to decide before the end of 2026. No FID as of 27 Sep 2026, so the tier stays advanced_proposed.</t>
+          <t>Final investment decision taken 29 September 2026 by the LNG Canada joint venture (Shell, PETRONAS, PetroChina, Mitsubishi, KOGAS); Fluor joint venture selected for engineering, procurement and construction. Moved from advanced_proposed.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3360,19 +3362,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>46294</v>
       </c>
       <c r="P11" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
@@ -3415,7 +3420,11 @@
         <v>3800</v>
       </c>
       <c r="AC11" s="4" t="inlineStr"/>
-      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>FID 29 Sep 2026; phase 2 cost reported at US$21–23bn (Mitsubishi share US$3.2bn implies US$21.3bn); total terminal capacity 28 mtpa; commercial operation expected in the early 2030s.</t>
+        </is>
+      </c>
       <c r="AF11" t="inlineStr">
         <is>
           <t>export</t>
@@ -3510,7 +3519,7 @@
       </c>
       <c r="BB11" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Major Projects Office, LNG Canada Phase 2: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki: https://www.gem.wiki/LNG_Canada_Terminal | The Northern View, Phase 2 decision could come as early as October (24 Sep 2026): https://thenorthernview.com/2026/09/24/lng-canada-phase-2-decision-could-come-as-early-as-october/</t>
+          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | NRCan Canadian LNG projects: https://natural-resources.canada.ca/energy-sources/fossil-fuels/canadian-liquified-natural-gas-projects | Major Projects Office, LNG Canada Phase 2: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html | CER Market Snapshot, Canada's future in LNG exports: https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2024/market-snapshot-exploring-canadas-future-in-lng-exports.html | Norton Rose Fulbright, Canadian LNG industry 2026 outlook: https://www.nortonrosefulbright.com/en/knowledge/publications/10bef30f/canadian-lng-industry-2026-outlook | GEM wiki: https://www.gem.wiki/LNG_Canada_Terminal | The Northern View, Phase 2 decision could come as early as October (24 Sep 2026): https://thenorthernview.com/2026/09/24/lng-canada-phase-2-decision-could-come-as-early-as-october/ | LNG Canada, LNG Canada Announces Phase 2 Final Investment Decision (Sep 2026): https://www.newswire.ca/news-releases/lng-canada-announces-phase-2-final-investment-decision-828313121.html | Shell, Shell takes final investment decision on LNG Canada Phase 2 (29 Sep 2026): https://news.europawire.eu/shell-takes-final-investment-decision-on-lng-canada-phase-2-to-double-kitimat-production-capacity-to-28-million-tonnes-per-year/eu-press-release/2026/09/29/14/54/00/181489/ | Financial Times, Shell-led consortium backs $23bn expansion of LNG Canada project (29 Sep 2026): https://www.ft.com/content/364d5454-876d-42ef-8f30-759e1ebdb026 | Fluor, Fluor joint venture selected for LNG Canada Phase 2 expansion following final investment decision (29 Sep 2026): https://www.financialcontent.com/article/bizwire-2026-9-29-fluor-joint-venture-selected-for-lng-canada-phase-2-expansion-following-final-investment-decision | TC Energy, Coastal GasLink Phase 2 to proceed following LNG Canada Final Investment Decision (29 Sep 2026): https://www.globenewswire.com/news-release/2026/09/29/3370625/0/en/coastal-gaslink-phase-2-to-proceed-following-lng-canada-final-investment-decision.html</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -13081,17 +13090,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Assigned by us from status, regulatory stage and FID - see tier_reason</t>
+          <t>Moved from advanced_proposed after the 29 Sep 2026 final investment decision. LNG Canada, LNG Canada Announces Phase 2 Final Investment Decision (Sep 2026): https://www.newswire.ca/news-releases/lng-canada-announces-phase-2-final-investment-decision-828313121.html</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Derived: advanced_proposed and early_proposed group as proposed</t>
+          <t>Follows tier after the 29 Sep 2026 final investment decision. Committed is operating plus under_construction.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Major Projects Office, LNG Canada Phase 2 (modified 2 Jul 2026): https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html | GEM wiki, LNG Canada Terminal (edited 25 Sep 2026): https://www.gem.wiki/LNG_Canada_Terminal | The Northern View, 24 Sep 2026 (Reuters): https://thenorthernview.com/2026/09/24/lng-canada-phase-2-decision-could-come-as-early-as-october/</t>
+          <t>Final investment decision taken 29 September 2026 by the LNG Canada joint venture (Shell, PETRONAS, PetroChina, Mitsubishi, KOGAS); Fluor joint venture selected for engineering, procurement and construction. Moved from advanced_proposed. LNG Canada, LNG Canada Announces Phase 2 Final Investment Decision (Sep 2026): https://www.newswire.ca/news-releases/lng-canada-announces-phase-2-final-investment-decision-828313121.html | Shell, Shell takes final investment decision on LNG Canada Phase 2 (29 Sep 2026): https://news.europawire.eu/shell-takes-final-investment-decision-on-lng-canada-phase-2-to-double-kitimat-production-capacity-to-28-million-tonnes-per-year/eu-press-release/2026/09/29/14/54/00/181489/ | Financial Times, Shell-led consortium backs $23bn expansion of LNG Canada project (29 Sep 2026): https://www.ft.com/content/364d5454-876d-42ef-8f30-759e1ebdb026 | Fluor, Fluor joint venture selected for LNG Canada Phase 2 expansion following final investment decision (29 Sep 2026): https://www.financialcontent.com/article/bizwire-2026-9-29-fluor-joint-venture-selected-for-lng-canada-phase-2-expansion-following-final-investment-decision | TC Energy, Coastal GasLink Phase 2 to proceed following LNG Canada Final Investment Decision (29 Sep 2026): https://www.globenewswire.com/news-release/2026/09/29/3370625/0/en/coastal-gaslink-phase-2-to-proceed-following-lng-canada-final-investment-decision.html</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -13116,7 +13125,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ (proposed); Major Projects Office, LNG Canada Phase 2: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html</t>
+          <t>Post-FID value used by Cedar LNG and Woodfibre LNG. Field Definitions: GEM status vocabulary operating, construction, proposed, shelved, cancelled. LNG Canada, LNG Canada Announces Phase 2 Final Investment Decision (Sep 2026): https://www.newswire.ca/news-releases/lng-canada-announces-phase-2-final-investment-decision-828313121.html</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -13126,17 +13135,17 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT LNG Terminals (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ FIDStatus=Pre-FID; FID targeted 2026 per Major Projects Office, LNG Canada Phase 2: https://www.canada.ca/en/privy-council/major-projects-office/projects/national/lng-canada.html</t>
+          <t>Final investment decision 29 Sep 2026. LNG Canada, LNG Canada Announces Phase 2 Final Investment Decision (Sep 2026): https://www.newswire.ca/news-releases/lng-canada-announces-phase-2-final-investment-decision-828313121.html | Shell, Shell takes final investment decision on LNG Canada Phase 2 (29 Sep 2026): https://news.europawire.eu/shell-takes-final-investment-decision-on-lng-canada-phase-2-to-double-kitimat-production-capacity-to-28-million-tonnes-per-year/eu-press-release/2026/09/29/14/54/00/181489/</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Announced 28 September 2026 Pacific time, 29 September 2026 UK time. LNG Canada, LNG Canada Announces Phase 2 Final Investment Decision (Sep 2026): https://www.newswire.ca/news-releases/lng-canada-announces-phase-2-final-investment-decision-828313121.html | Shell, Shell takes final investment decision on LNG Canada Phase 2 (29 Sep 2026): https://news.europawire.eu/shell-takes-final-investment-decision-on-lng-canada-phase-2-to-double-kitimat-production-capacity-to-28-million-tonnes-per-year/eu-press-release/2026/09/29/14/54/00/181489/</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>GEM wiki, LNG Canada Terminal (edited 25 Sep 2026): https://www.gem.wiki/LNG_Canada_Terminal - planned first LNG for Phase 2 is 2030. Unchanged from GEM GGIT (Sep 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ LatestPlannedStartYear=2030. No developer date published; replace with the date given at FID.</t>
+          <t>2031: decision date September 2026 plus the IEA's 4 to 5 year lag from final investment decision to completion (Parameters post_fid_to_completion = 4.5), consistent with Shell's statement that commercial operations are expected in the early 2030s. Decision 29 Sep 2026. Shell, Shell takes final investment decision on LNG Canada Phase 2 (29 Sep 2026): https://news.europawire.eu/shell-takes-final-investment-decision-on-lng-canada-phase-2-to-double-kitimat-production-capacity-to-28-million-tonnes-per-year/eu-press-release/2026/09/29/14/54/00/181489/</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -13211,7 +13220,7 @@
       </c>
       <c r="AE11" s="4" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>FID 29 Sep 2026; phase 2 cost reported at US$21–23bn (Mitsubishi share US$3.2bn implies US$21.3bn); total terminal capacity 28 mtpa; commercial operation expected in the early 2030s. LNG Canada, LNG Canada Announces Phase 2 Final Investment Decision (Sep 2026): https://www.newswire.ca/news-releases/lng-canada-announces-phase-2-final-investment-decision-828313121.html | Shell, Shell takes final investment decision on LNG Canada Phase 2 (29 Sep 2026): https://news.europawire.eu/shell-takes-final-investment-decision-on-lng-canada-phase-2-to-double-kitimat-production-capacity-to-28-million-tonnes-per-year/eu-press-release/2026/09/29/14/54/00/181489/ | Financial Times, Shell-led consortium backs $23bn expansion of LNG Canada project (29 Sep 2026): https://www.ft.com/content/364d5454-876d-42ef-8f30-759e1ebdb026</t>
         </is>
       </c>
       <c r="AF11" s="4" t="inlineStr">
@@ -28445,12 +28454,12 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>The single largest piece of new gas infrastructure proposed in Canada. LNG Canada and the Coastal GasLink owners agreed in March 2026 to cooperate on expanding capacity. Phase 2 cannot physically run without it.</t>
+          <t>The single largest piece of new gas infrastructure proposed in Canada. LNG Canada and the Coastal GasLink owners agreed in March 2026 to cooperate on expanding capacity. Phase 2 cannot physically run without it. Phase 2 expansion to proceed following the LNG Canada Phase 2 FID (29 Sep 2026)</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>GEM GGIT Gas Pipelines (Nov 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/</t>
+          <t>GEM GGIT Gas Pipelines (Nov 2025): https://globalenergymonitor.org/projects/global-gas-infrastructure-tracker/ | TC Energy, Coastal GasLink Phase 2 to proceed following LNG Canada Final Investment Decision (29 Sep 2026): https://www.globenewswire.com/news-release/2026/09/29/3370625/0/en/coastal-gaslink-phase-2-to-proceed-following-lng-canada-final-investment-decision.html</t>
         </is>
       </c>
     </row>
